--- a/04_Figures/F06_prediction/modules/T1/enet/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T1/enet/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -146,34 +146,37 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_yellow</t>
+    <t xml:space="preserve">ME_black</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_black</t>
+    <t xml:space="preserve">ME_blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_greenyellow</t>
   </si>
   <si>
     <t xml:space="preserve">ME_magenta</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon</t>
+    <t xml:space="preserve">ME_pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_red</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_greenyellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
+    <t xml:space="preserve">ME_yellow</t>
   </si>
 </sst>
 </file>
@@ -560,13 +563,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.172814069484104</v>
       </c>
       <c r="I2" t="n">
         <v>-1</v>
@@ -593,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.172814069484104</v>
       </c>
       <c r="I3" t="n">
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.208955223880597</v>
+        <v>0.388059701492537</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.391742232678428</v>
+        <v>-0.728394346792915</v>
       </c>
       <c r="M3" t="n">
-        <v>0.73212801851951</v>
+        <v>1.8398728056215</v>
       </c>
     </row>
     <row r="4">
@@ -634,7 +637,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -667,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -679,16 +682,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3681592039801</v>
+        <v>0.308457711442786</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.380042734050054</v>
+        <v>-0.568991049993462</v>
       </c>
       <c r="M5" t="n">
-        <v>0.558296357709312</v>
+        <v>1.60637988855578</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +711,16 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.14795918367347</v>
+        <v>-6.16465104866151</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-0.667857142857143</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -741,28 +744,28 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.14795918367347</v>
+        <v>-6.16465104866151</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>-0.667857142857143</v>
       </c>
       <c r="J7" t="n">
-        <v>0.462686567164179</v>
+        <v>0.995024875621891</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.223880597014925</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.412226921029472</v>
+        <v>-0.459963968727985</v>
       </c>
       <c r="M7" t="n">
-        <v>0.662631447309513</v>
+        <v>0.867403807563798</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -815,7 +818,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
@@ -827,16 +830,16 @@
         <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.323383084577114</v>
+        <v>0.338308457711443</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.394473560035112</v>
+        <v>-0.534857664210987</v>
       </c>
       <c r="M9" t="n">
-        <v>0.599337137555968</v>
+        <v>0.91616170333139</v>
       </c>
     </row>
     <row r="10">
@@ -856,16 +859,16 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.363631084898001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>-0.802158273381295</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -889,28 +892,28 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.363631084898001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1</v>
+        <v>-0.802158273381295</v>
       </c>
       <c r="J11" t="n">
-        <v>0.218905472636816</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.258706467661692</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.379270104235187</v>
+        <v>-0.672925170902839</v>
       </c>
       <c r="M11" t="n">
-        <v>0.490494300889986</v>
+        <v>1.4425010059165</v>
       </c>
     </row>
     <row r="12">
@@ -930,16 +933,16 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.521132772675237</v>
+        <v>-5.34900300374593</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.820287157881069</v>
+        <v>-0.53142259421865</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -963,28 +966,28 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.521132772675237</v>
+        <v>-5.34900300374593</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.820287157881069</v>
+        <v>-0.53142259421865</v>
       </c>
       <c r="J13" t="n">
-        <v>0.805970149253731</v>
+        <v>0.985074626865672</v>
       </c>
       <c r="K13" t="n">
-        <v>0.189054726368159</v>
+        <v>0.104477611940299</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.350252173999844</v>
+        <v>-0.560871017645385</v>
       </c>
       <c r="M13" t="n">
-        <v>0.425444404937599</v>
+        <v>1.6284905424457</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.9840786790917</v>
+        <v>-0.174207280165866</v>
       </c>
     </row>
     <row r="3">
@@ -1039,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.968671836837315</v>
+        <v>-0.581523107504554</v>
       </c>
     </row>
     <row r="5">
@@ -1050,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.19271169685049</v>
+        <v>-0.236187381329404</v>
       </c>
     </row>
     <row r="6">
@@ -1061,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>0.51052320551916</v>
+        <v>0.11396324749432</v>
       </c>
     </row>
     <row r="7">
@@ -1072,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.498050255155175</v>
+        <v>-1.83898578396652</v>
       </c>
     </row>
     <row r="8">
@@ -1083,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.25621560644253</v>
       </c>
     </row>
     <row r="9">
@@ -1094,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>0.23402514583713</v>
+        <v>-0.614294148225746</v>
       </c>
     </row>
     <row r="10">
@@ -1105,7 +1108,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.265033521473567</v>
+        <v>-0.209261412485595</v>
       </c>
     </row>
     <row r="11">
@@ -1116,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.198947431513238</v>
+        <v>-0.230542423110362</v>
       </c>
     </row>
     <row r="12">
@@ -1127,7 +1130,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.17616521347427</v>
+        <v>-0.19446223884616</v>
       </c>
     </row>
     <row r="13">
@@ -1149,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.670733140598124</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="15">
@@ -1160,7 +1163,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.22420078752639</v>
       </c>
     </row>
     <row r="16">
@@ -1171,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.173932418682425</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="17">
@@ -1182,7 +1185,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.212032137259912</v>
       </c>
     </row>
     <row r="18">
@@ -1204,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>0.223500003687045</v>
+        <v>-0.651324720629601</v>
       </c>
     </row>
     <row r="20">
@@ -1215,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00886421310470664</v>
+        <v>0.029770262011652</v>
       </c>
     </row>
     <row r="21">
@@ -1226,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.605754797082148</v>
       </c>
     </row>
     <row r="22">
@@ -1237,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.156656214043579</v>
+        <v>-0.468932986287573</v>
       </c>
     </row>
     <row r="23">
@@ -1248,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.355061979117625</v>
       </c>
     </row>
     <row r="24">
@@ -1259,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.902904551136835</v>
       </c>
     </row>
     <row r="25">
@@ -1270,7 +1273,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.166392897900427</v>
+        <v>-0.195210949455088</v>
       </c>
     </row>
     <row r="26">
@@ -1281,7 +1284,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.411390244194736</v>
+        <v>-0.199456941324766</v>
       </c>
     </row>
     <row r="27">
@@ -1314,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.11412312672731</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="30">
@@ -1325,7 +1328,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.355266535094999</v>
       </c>
     </row>
     <row r="31">
@@ -1336,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.168246207143457</v>
+        <v>-0.639325996121529</v>
       </c>
     </row>
     <row r="32">
@@ -1347,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.200412170357974</v>
+        <v>0.0244779872744274</v>
       </c>
     </row>
     <row r="33">
@@ -1369,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.323104726418752</v>
+        <v>-0.263082423479133</v>
       </c>
     </row>
     <row r="35">
@@ -1391,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.675052125739978</v>
       </c>
     </row>
     <row r="37">
@@ -1402,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0599440935215827</v>
+        <v>-0.314967441139497</v>
       </c>
     </row>
     <row r="38">
@@ -1424,7 +1427,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.253930441598676</v>
       </c>
     </row>
     <row r="40">
@@ -1435,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>0.222018700014388</v>
+        <v>-0.314147576823498</v>
       </c>
     </row>
     <row r="41">
@@ -1446,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.174762319454379</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="42">
@@ -1457,7 +1460,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.182065950375931</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="43">
@@ -1468,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.128476396546448</v>
+        <v>-0.834692799896766</v>
       </c>
     </row>
     <row r="44">
@@ -1479,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.86392045424833</v>
       </c>
     </row>
     <row r="45">
@@ -1490,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0727712556197324</v>
+        <v>0.606044790443089</v>
       </c>
     </row>
     <row r="46">
@@ -1501,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.24750950956645</v>
+        <v>-0.382472076296127</v>
       </c>
     </row>
     <row r="47">
@@ -1512,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.483213547954468</v>
+        <v>-2.01776407377898</v>
       </c>
     </row>
     <row r="48">
@@ -1523,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.393277891608087</v>
+        <v>-0.257662801314261</v>
       </c>
     </row>
     <row r="49">
@@ -1534,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.404433139862587</v>
+        <v>-0.779835003579321</v>
       </c>
     </row>
     <row r="50">
@@ -1545,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0938876024839217</v>
+        <v>-0.0850981399976971</v>
       </c>
     </row>
     <row r="51">
@@ -1556,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.097278048448447</v>
+        <v>-0.547416008597937</v>
       </c>
     </row>
     <row r="52">
@@ -1567,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0644773233552403</v>
+        <v>0.0966256041892924</v>
       </c>
     </row>
     <row r="53">
@@ -1589,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.819094526831978</v>
+        <v>-1.84219509898876</v>
       </c>
     </row>
     <row r="55">
@@ -1600,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.323220625437881</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="56">
@@ -1611,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-5.7942220763987</v>
+        <v>-1.40492561837469</v>
       </c>
     </row>
     <row r="57">
@@ -1622,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0498463978582138</v>
+        <v>-0.422450073222496</v>
       </c>
     </row>
     <row r="58">
@@ -1633,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-2.61637705075295</v>
+        <v>-1.25359560966271</v>
       </c>
     </row>
     <row r="59">
@@ -1644,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.24131147972144</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="60">
@@ -1666,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.664209418892621</v>
       </c>
     </row>
     <row r="62">
@@ -1677,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.596567250254148</v>
+        <v>-2.04225304360732</v>
       </c>
     </row>
     <row r="63">
@@ -1688,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.685466101617322</v>
+        <v>-0.982119701194673</v>
       </c>
     </row>
     <row r="64">
@@ -1699,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.197916994798989</v>
+        <v>-2.49531964509817</v>
       </c>
     </row>
     <row r="65">
@@ -1710,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.237748494832814</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="66">
@@ -1721,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.670724789534423</v>
+        <v>-0.449990049436443</v>
       </c>
     </row>
     <row r="67">
@@ -1732,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>0.040174637469295</v>
+        <v>-0.643757354071345</v>
       </c>
     </row>
     <row r="68">
@@ -1743,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.16025222817717</v>
+        <v>-0.1318803297273</v>
       </c>
     </row>
     <row r="69">
@@ -1754,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.223573184890596</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="70">
@@ -1765,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.195202147248402</v>
+        <v>-0.235149112469971</v>
       </c>
     </row>
     <row r="71">
@@ -1787,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.226335715612335</v>
+        <v>-0.522689783263027</v>
       </c>
     </row>
     <row r="73">
@@ -1798,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.644467940518718</v>
+        <v>-0.530413121083747</v>
       </c>
     </row>
     <row r="74">
@@ -1809,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.420394224355655</v>
+        <v>-0.980921212701693</v>
       </c>
     </row>
     <row r="75">
@@ -1820,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>0.894583570270915</v>
+        <v>-0.0412227209253433</v>
       </c>
     </row>
     <row r="76">
@@ -1831,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.268444486089256</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="77">
@@ -1842,7 +1845,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.497313907560261</v>
+        <v>0.59988131407073</v>
       </c>
     </row>
     <row r="78">
@@ -1853,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.402166913191356</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="79">
@@ -1864,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.393474309197327</v>
+        <v>-0.214350054476253</v>
       </c>
     </row>
     <row r="80">
@@ -1875,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.601887650610548</v>
       </c>
     </row>
     <row r="81">
@@ -1886,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>0.354792018461652</v>
+        <v>-1.16677092067405</v>
       </c>
     </row>
     <row r="82">
@@ -1897,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.29776794449434</v>
+        <v>-0.295743678833232</v>
       </c>
     </row>
     <row r="83">
@@ -1908,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.07861867949426</v>
       </c>
     </row>
     <row r="84">
@@ -1930,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.759409858415316</v>
+        <v>-1.11836833699551</v>
       </c>
     </row>
     <row r="86">
@@ -1941,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>0.191097485237637</v>
+        <v>0.162582126972618</v>
       </c>
     </row>
     <row r="87">
@@ -1952,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-1.41191302321347</v>
+        <v>-0.26193762125825</v>
       </c>
     </row>
     <row r="88">
@@ -1963,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.2167392006205</v>
+        <v>-0.17436124949699</v>
       </c>
     </row>
     <row r="89">
@@ -1974,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.0961944623562558</v>
+        <v>-0.584098274791676</v>
       </c>
     </row>
     <row r="90">
@@ -1985,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.786263266578159</v>
+        <v>-0.383376838210864</v>
       </c>
     </row>
     <row r="91">
@@ -1996,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.402452180219845</v>
+        <v>-0.373897630251387</v>
       </c>
     </row>
     <row r="92">
@@ -2007,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.212272817700391</v>
+        <v>-0.242845836392748</v>
       </c>
     </row>
     <row r="93">
@@ -2018,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>0.330393000773317</v>
+        <v>-0.270821782768381</v>
       </c>
     </row>
     <row r="94">
@@ -2029,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.65443594370568</v>
+        <v>-0.233393954948915</v>
       </c>
     </row>
     <row r="95">
@@ -2040,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.485488147960637</v>
+        <v>-0.318339033163044</v>
       </c>
     </row>
     <row r="96">
@@ -2051,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>0.104881516879996</v>
+        <v>0.176324131018795</v>
       </c>
     </row>
     <row r="97">
@@ -2073,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-2.4505403735994</v>
+        <v>-3.23916363530411</v>
       </c>
     </row>
     <row r="99">
@@ -2084,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.364623739450556</v>
+        <v>-0.180496853663318</v>
       </c>
     </row>
     <row r="100">
@@ -2095,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>0.092236405636217</v>
+        <v>-0.271077550896419</v>
       </c>
     </row>
     <row r="101">
@@ -2139,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>0.131019441646276</v>
+        <v>-0.218276192613662</v>
       </c>
     </row>
     <row r="105">
@@ -2150,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.349488323566115</v>
+        <v>-0.354199767883064</v>
       </c>
     </row>
     <row r="106">
@@ -2161,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.828782252523943</v>
       </c>
     </row>
     <row r="107">
@@ -2172,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.390509447363199</v>
       </c>
     </row>
     <row r="108">
@@ -2183,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.07675032159641</v>
       </c>
     </row>
     <row r="109">
@@ -2194,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0424257960282752</v>
+        <v>-0.0892914265802318</v>
       </c>
     </row>
     <row r="110">
@@ -2205,7 +2208,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.602191877040094</v>
       </c>
     </row>
     <row r="111">
@@ -2227,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.732970339646182</v>
       </c>
     </row>
     <row r="113">
@@ -2238,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.24799752371763</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="114">
@@ -2249,7 +2252,7 @@
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>-1.50157885422727</v>
+        <v>-0.137961480610631</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.180091109341917</v>
+        <v>-0.514014412261866</v>
       </c>
     </row>
     <row r="117">
@@ -2282,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.63667319290848</v>
+        <v>-0.28400275642938</v>
       </c>
     </row>
     <row r="118">
@@ -2293,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.521411327543832</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="119">
@@ -2304,7 +2307,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.426824239937141</v>
+        <v>-1.69184887407965</v>
       </c>
     </row>
     <row r="120">
@@ -2326,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.287489505359004</v>
+        <v>-0.120653218010517</v>
       </c>
     </row>
     <row r="122">
@@ -2348,7 +2351,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.71426871973078</v>
       </c>
     </row>
     <row r="124">
@@ -2359,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-1.22357169233305</v>
+        <v>-0.378930814930594</v>
       </c>
     </row>
     <row r="125">
@@ -2370,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.406099512383</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="126">
@@ -2381,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.183812322934644</v>
+        <v>-6.94799443538119</v>
       </c>
     </row>
     <row r="127">
@@ -2403,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>0.244099744344819</v>
+        <v>-0.357857434606583</v>
       </c>
     </row>
     <row r="129">
@@ -2414,7 +2417,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.114722948063392</v>
+        <v>-0.205277221455271</v>
       </c>
     </row>
     <row r="130">
@@ -2425,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.0286529921077199</v>
+        <v>0.107768960714278</v>
       </c>
     </row>
     <row r="131">
@@ -2436,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.308075665658388</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="132">
@@ -2447,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.509611578332299</v>
+        <v>-0.979162576028233</v>
       </c>
     </row>
     <row r="133">
@@ -2458,7 +2461,7 @@
         <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.583010369627684</v>
+        <v>-0.669760863948125</v>
       </c>
     </row>
     <row r="134">
@@ -2469,7 +2472,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.506109534516191</v>
       </c>
     </row>
     <row r="135">
@@ -2480,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>0.470798847175829</v>
+        <v>-0.996480105510804</v>
       </c>
     </row>
     <row r="136">
@@ -2491,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>0.211871756333275</v>
+        <v>-0.185816060741944</v>
       </c>
     </row>
     <row r="137">
@@ -2513,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.395168663538756</v>
+        <v>-0.426943465596538</v>
       </c>
     </row>
     <row r="139">
@@ -2524,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.395921865333667</v>
+        <v>-0.417053430969433</v>
       </c>
     </row>
     <row r="140">
@@ -2535,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.375512626562065</v>
+        <v>-0.288434542274305</v>
       </c>
     </row>
     <row r="141">
@@ -2546,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.18297004932603</v>
+        <v>-0.939557115041363</v>
       </c>
     </row>
     <row r="142">
@@ -2557,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.713474326996368</v>
+        <v>-13.3867826056039</v>
       </c>
     </row>
     <row r="143">
@@ -2579,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.23380305533252</v>
+        <v>-0.170362856601422</v>
       </c>
     </row>
     <row r="145">
@@ -2590,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.0561089191344442</v>
+        <v>-0.634959563844979</v>
       </c>
     </row>
     <row r="146">
@@ -2612,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.599951732452803</v>
+        <v>-2.10747656667176</v>
       </c>
     </row>
     <row r="148">
@@ -2623,7 +2626,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.471568865467691</v>
       </c>
     </row>
     <row r="149">
@@ -2634,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.21719463851369</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="150">
@@ -2645,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.282749851036356</v>
+        <v>-0.224488074305123</v>
       </c>
     </row>
     <row r="151">
@@ -2667,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.75588219793292</v>
+        <v>-0.198772895573579</v>
       </c>
     </row>
     <row r="153">
@@ -2678,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.320378387503653</v>
+        <v>-0.243794286584283</v>
       </c>
     </row>
     <row r="154">
@@ -2700,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.93552641847477</v>
       </c>
     </row>
     <row r="156">
@@ -2711,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.163036254514015</v>
+        <v>0.0600927427223975</v>
       </c>
     </row>
     <row r="157">
@@ -2722,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.511790509397938</v>
       </c>
     </row>
     <row r="158">
@@ -2733,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.717857354683969</v>
+        <v>-0.692709792194999</v>
       </c>
     </row>
     <row r="159">
@@ -2744,7 +2747,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="n">
-        <v>0.295586451947334</v>
+        <v>0.331297081924623</v>
       </c>
     </row>
     <row r="160">
@@ -2755,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.271224610604726</v>
+        <v>-0.616189957218483</v>
       </c>
     </row>
     <row r="161">
@@ -2766,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.181851174646032</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="162">
@@ -2777,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.35403943880546</v>
+        <v>0.204708327830405</v>
       </c>
     </row>
     <row r="163">
@@ -2788,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.193510921330285</v>
+        <v>-0.157772952939209</v>
       </c>
     </row>
     <row r="164">
@@ -2799,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0252318360350343</v>
+        <v>-2.77113768643791</v>
       </c>
     </row>
     <row r="165">
@@ -2810,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.128864818557751</v>
+        <v>-0.300160725520157</v>
       </c>
     </row>
     <row r="166">
@@ -2821,7 +2824,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.141002003515631</v>
       </c>
     </row>
     <row r="167">
@@ -2843,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.262165914817557</v>
+        <v>-2.14710941974679</v>
       </c>
     </row>
     <row r="169">
@@ -2854,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.4022170334871</v>
       </c>
     </row>
     <row r="170">
@@ -2865,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.543446908642913</v>
+        <v>-0.727289327375688</v>
       </c>
     </row>
     <row r="171">
@@ -2876,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-3.32834048945242</v>
+        <v>-0.678326553659891</v>
       </c>
     </row>
     <row r="172">
@@ -2887,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.147959183673469</v>
+        <v>-18.7302179355713</v>
       </c>
     </row>
     <row r="173">
@@ -2898,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.303424974696149</v>
       </c>
     </row>
     <row r="174">
@@ -2909,7 +2912,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-1.25500683023795</v>
+        <v>-0.574651558051787</v>
       </c>
     </row>
     <row r="175">
@@ -2920,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.250062614302957</v>
+        <v>-0.270998503655383</v>
       </c>
     </row>
     <row r="176">
@@ -2931,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-1.20934407938479</v>
+        <v>-1.37252185977397</v>
       </c>
     </row>
     <row r="177">
@@ -2953,7 +2956,7 @@
         <v>16</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.164039670806835</v>
       </c>
     </row>
     <row r="179">
@@ -2964,7 +2967,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.684513804290649</v>
+        <v>-0.901178141520938</v>
       </c>
     </row>
     <row r="180">
@@ -2975,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>0.26309394726309</v>
+        <v>0.183684287440601</v>
       </c>
     </row>
     <row r="181">
@@ -2986,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.266727877194105</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="182">
@@ -2997,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>0.12467335963914</v>
+        <v>-0.285420651193949</v>
       </c>
     </row>
     <row r="183">
@@ -3008,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-4.39802285687231</v>
+        <v>-0.806009014778722</v>
       </c>
     </row>
     <row r="184">
@@ -3019,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.364746135958635</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="185">
@@ -3030,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.190796222537295</v>
+        <v>-0.194083274299309</v>
       </c>
     </row>
     <row r="186">
@@ -3041,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.3032971279454</v>
+        <v>-5.64493401097586</v>
       </c>
     </row>
     <row r="187">
@@ -3074,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.296681827953029</v>
+        <v>-0.588226130342374</v>
       </c>
     </row>
     <row r="190">
@@ -3085,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.320211062536663</v>
+        <v>-0.519106609344868</v>
       </c>
     </row>
     <row r="191">
@@ -3096,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.684329048596315</v>
+        <v>-0.469022674404806</v>
       </c>
     </row>
     <row r="192">
@@ -3107,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.626686211951961</v>
+        <v>-1.53793239759034</v>
       </c>
     </row>
     <row r="193">
@@ -3118,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-1.73901412821155</v>
+        <v>-0.366047241675643</v>
       </c>
     </row>
     <row r="194">
@@ -3129,7 +3132,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-1.84340216829816</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="195">
@@ -3140,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>0.0818758099674265</v>
+        <v>0.269211282979166</v>
       </c>
     </row>
     <row r="196">
@@ -3151,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.444106147383634</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="197">
@@ -3162,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>0.173739375886873</v>
+        <v>-0.373617975935942</v>
       </c>
     </row>
     <row r="198">
@@ -3173,7 +3176,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.498050200398629</v>
+        <v>-0.623346410437363</v>
       </c>
     </row>
     <row r="199">
@@ -3184,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-3.1386032535354</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="200">
@@ -3195,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.205231585530713</v>
       </c>
     </row>
     <row r="201">
@@ -3206,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>0.404277491743982</v>
+        <v>-0.0590419475175927</v>
       </c>
     </row>
     <row r="202">
@@ -3217,7 +3220,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.140962479378601</v>
+        <v>-0.169875007753201</v>
       </c>
     </row>
     <row r="203">
@@ -3239,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-1.02055704033879</v>
+        <v>-1.25968352081367</v>
       </c>
     </row>
     <row r="205">
@@ -3250,7 +3253,7 @@
         <v>16</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.147949195602499</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="206">
@@ -3261,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.206017241691988</v>
+        <v>-0.289692016827868</v>
       </c>
     </row>
     <row r="207">
@@ -3272,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.591913161239929</v>
+        <v>-0.667667530510885</v>
       </c>
     </row>
     <row r="208">
@@ -3283,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.66456939407964</v>
       </c>
     </row>
     <row r="209">
@@ -3294,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.485686017073239</v>
+        <v>-0.155205095939501</v>
       </c>
     </row>
     <row r="210">
@@ -3316,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.44389911624389</v>
+        <v>-3.02579584482809</v>
       </c>
     </row>
     <row r="212">
@@ -3327,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.166842613068768</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="213">
@@ -3338,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.957839815932046</v>
       </c>
     </row>
     <row r="214">
@@ -3349,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.345775915226893</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="215">
@@ -3360,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.33072701243517</v>
       </c>
     </row>
     <row r="216">
@@ -3371,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-1.14158615364532</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="217">
@@ -3382,7 +3385,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.808765475453652</v>
+        <v>-0.359059607038212</v>
       </c>
     </row>
     <row r="218">
@@ -3393,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.868155056429595</v>
       </c>
     </row>
     <row r="219">
@@ -3404,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.233029942750371</v>
+        <v>-0.423993410161348</v>
       </c>
     </row>
     <row r="220">
@@ -3415,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.858892278596687</v>
+        <v>0.062406559101466</v>
       </c>
     </row>
     <row r="221">
@@ -3448,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.408917444763204</v>
       </c>
     </row>
     <row r="224">
@@ -3459,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.83694300653816</v>
       </c>
     </row>
     <row r="225">
@@ -3481,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.728130841426482</v>
+        <v>-0.239771564442832</v>
       </c>
     </row>
     <row r="227">
@@ -3514,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.736765641898561</v>
+        <v>-0.267379978705849</v>
       </c>
     </row>
     <row r="230">
@@ -3536,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.256742739897348</v>
+        <v>-1.02526859140289</v>
       </c>
     </row>
     <row r="232">
@@ -3547,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.424804403607391</v>
+        <v>-0.257339107159616</v>
       </c>
     </row>
     <row r="233">
@@ -3558,7 +3561,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.175444579118577</v>
       </c>
     </row>
     <row r="234">
@@ -3569,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.102992674230372</v>
+        <v>-0.00637946567572567</v>
       </c>
     </row>
     <row r="235">
@@ -3591,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.236904491019423</v>
+        <v>-0.775983938804056</v>
       </c>
     </row>
     <row r="237">
@@ -3602,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.136865758811764</v>
+        <v>-0.890238009663598</v>
       </c>
     </row>
     <row r="238">
@@ -3613,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-1.73298781707844</v>
+        <v>-1.20357763597083</v>
       </c>
     </row>
     <row r="239">
@@ -3624,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.275703030343929</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="240">
@@ -3635,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.38159311800981</v>
+        <v>-0.185456478785632</v>
       </c>
     </row>
     <row r="241">
@@ -3657,7 +3660,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="n">
-        <v>-3.15691538945984</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="243">
@@ -3668,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.536633244872766</v>
+        <v>-0.981827018287288</v>
       </c>
     </row>
     <row r="244">
@@ -3690,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.236338617229876</v>
+        <v>-0.710959148288954</v>
       </c>
     </row>
     <row r="246">
@@ -3701,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.879454846001684</v>
+        <v>-0.685672150979379</v>
       </c>
     </row>
     <row r="247">
@@ -3712,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.260596789907956</v>
+        <v>-0.363567698549109</v>
       </c>
     </row>
     <row r="248">
@@ -3723,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.18974575891216</v>
+        <v>-0.20037977157449</v>
       </c>
     </row>
     <row r="249">
@@ -3734,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.262868289841431</v>
+        <v>-0.628252371349598</v>
       </c>
     </row>
     <row r="250">
@@ -3745,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.147959183673469</v>
+        <v>-21.7214877661859</v>
       </c>
     </row>
     <row r="251">
@@ -3756,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.1795039138585</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="252">
@@ -3767,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.388835045032383</v>
+        <v>-1.10464737937863</v>
       </c>
     </row>
     <row r="253">
@@ -3778,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.182253911680948</v>
+        <v>-0.206341180257424</v>
       </c>
     </row>
     <row r="254">
@@ -3789,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.38778940708852</v>
       </c>
     </row>
     <row r="255">
@@ -3800,7 +3803,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.305638227742036</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="256">
@@ -3811,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.847908372515674</v>
+        <v>-0.183448471071648</v>
       </c>
     </row>
     <row r="257">
@@ -3822,7 +3825,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.0743275600813382</v>
+        <v>-0.582897747481222</v>
       </c>
     </row>
     <row r="258">
@@ -3833,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.285694139800195</v>
+        <v>-0.334645158724279</v>
       </c>
     </row>
     <row r="259">
@@ -3855,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.239077298301479</v>
+        <v>-0.165720212377917</v>
       </c>
     </row>
     <row r="261">
@@ -3877,7 +3880,7 @@
         <v>16</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.321144340270526</v>
+        <v>-0.475214292646282</v>
       </c>
     </row>
     <row r="263">
@@ -3888,7 +3891,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.830218475051701</v>
+        <v>-0.494097186750138</v>
       </c>
     </row>
     <row r="264">
@@ -3899,7 +3902,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.372089399985382</v>
+        <v>-0.256744212294605</v>
       </c>
     </row>
     <row r="265">
@@ -3910,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.278930730189366</v>
       </c>
     </row>
     <row r="266">
@@ -3921,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.993859331886586</v>
+        <v>-0.190125936380059</v>
       </c>
     </row>
     <row r="267">
@@ -3932,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.846409136982917</v>
+        <v>-1.10277759386336</v>
       </c>
     </row>
     <row r="268">
@@ -3943,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>0.140297609198516</v>
+        <v>0.130023713306908</v>
       </c>
     </row>
     <row r="269">
@@ -3954,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.326589622322053</v>
+        <v>-0.437073652343884</v>
       </c>
     </row>
     <row r="270">
@@ -3965,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.310153751200336</v>
+        <v>-0.226992548705448</v>
       </c>
     </row>
     <row r="271">
@@ -3976,7 +3979,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.761524758092113</v>
+        <v>-1.50272483977292</v>
       </c>
     </row>
     <row r="272">
@@ -3998,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.195561827558123</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="274">
@@ -4009,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.496273874386668</v>
+        <v>-0.433627803071484</v>
       </c>
     </row>
     <row r="275">
@@ -4020,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.390851097736396</v>
+        <v>-0.563638769300302</v>
       </c>
     </row>
     <row r="276">
@@ -4042,7 +4045,7 @@
         <v>16</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.43541790560423</v>
+        <v>-0.319159983591528</v>
       </c>
     </row>
     <row r="278">
@@ -4053,7 +4056,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="n">
-        <v>-2.05465609784448</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="279">
@@ -4064,7 +4067,7 @@
         <v>16</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.102456165547869</v>
+        <v>-0.387830331764799</v>
       </c>
     </row>
     <row r="280">
@@ -4086,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>0.052626389769953</v>
+        <v>0.0762824695930421</v>
       </c>
     </row>
     <row r="282">
@@ -4097,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.247840603169039</v>
+        <v>0.694537716393658</v>
       </c>
     </row>
     <row r="283">
@@ -4119,7 +4122,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-1.24072574658621</v>
+        <v>-0.744738760118018</v>
       </c>
     </row>
     <row r="285">
@@ -4130,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.78609087245889</v>
+        <v>-0.538270535471558</v>
       </c>
     </row>
     <row r="286">
@@ -4141,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>0.146876712368417</v>
+        <v>0.615343364024665</v>
       </c>
     </row>
     <row r="287">
@@ -4152,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-1.39684044518398</v>
+        <v>-2.44595520289643</v>
       </c>
     </row>
     <row r="288">
@@ -4163,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.292830852355076</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.0421902980352584</v>
+        <v>-0.340685897770345</v>
       </c>
     </row>
     <row r="290">
@@ -4185,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>0.0736608398077517</v>
+        <v>-1.46274908971808</v>
       </c>
     </row>
     <row r="291">
@@ -4196,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.683483910663081</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="292">
@@ -4218,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>0.0265910064956608</v>
+        <v>-1.237078864692</v>
       </c>
     </row>
     <row r="294">
@@ -4240,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.823268257937582</v>
+        <v>-0.81001803171713</v>
       </c>
     </row>
     <row r="296">
@@ -4251,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>0.201066995057187</v>
+        <v>0.322740428691049</v>
       </c>
     </row>
     <row r="297">
@@ -4262,7 +4265,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.2280974443255</v>
       </c>
     </row>
     <row r="298">
@@ -4273,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.178876470076821</v>
       </c>
     </row>
     <row r="299">
@@ -4284,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>0.307059892341052</v>
+        <v>0.11123091432317</v>
       </c>
     </row>
     <row r="300">
@@ -4295,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>0.315982002454988</v>
+        <v>-0.665185407822664</v>
       </c>
     </row>
     <row r="301">
@@ -4328,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.00347618513502</v>
       </c>
     </row>
     <row r="304">
@@ -4339,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-1.35825185756029</v>
+        <v>-0.89284083717835</v>
       </c>
     </row>
     <row r="305">
@@ -4350,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.472848754602647</v>
+        <v>-1.26358244975075</v>
       </c>
     </row>
     <row r="306">
@@ -4361,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.44139398278464</v>
       </c>
     </row>
     <row r="307">
@@ -4372,7 +4375,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.396872411142944</v>
       </c>
     </row>
     <row r="308">
@@ -4394,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.472034709889311</v>
+        <v>-0.215623918781938</v>
       </c>
     </row>
     <row r="310">
@@ -4416,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-3.55018496096303</v>
+        <v>-0.158926767623102</v>
       </c>
     </row>
     <row r="312">
@@ -4427,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.249551603367161</v>
+        <v>-0.25272180482698</v>
       </c>
     </row>
     <row r="313">
@@ -4438,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.238618549913451</v>
+        <v>-0.343506498129664</v>
       </c>
     </row>
     <row r="314">
@@ -4449,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-2.55978556819797</v>
+        <v>-0.702741062305451</v>
       </c>
     </row>
     <row r="315">
@@ -4460,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-1.31273099179693</v>
+        <v>-0.6368939109771</v>
       </c>
     </row>
     <row r="316">
@@ -4471,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.336819869032484</v>
+        <v>-0.287910374176382</v>
       </c>
     </row>
     <row r="317">
@@ -4482,7 +4485,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.45964551386059</v>
+        <v>-3.2136881258985</v>
       </c>
     </row>
     <row r="318">
@@ -4493,7 +4496,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-1.29201213621856</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="319">
@@ -4504,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.803031664722481</v>
+        <v>-2.08876775986479</v>
       </c>
     </row>
     <row r="320">
@@ -4515,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.44830428540593</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="321">
@@ -4526,7 +4529,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.199999273819132</v>
+        <v>-0.178725381197969</v>
       </c>
     </row>
     <row r="322">
@@ -4537,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.397843449498795</v>
       </c>
     </row>
     <row r="323">
@@ -4548,7 +4551,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.213424941161081</v>
+        <v>-0.245966334062832</v>
       </c>
     </row>
     <row r="324">
@@ -4559,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.325266452177447</v>
+        <v>-1.17288828418427</v>
       </c>
     </row>
     <row r="325">
@@ -4570,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.344498463050819</v>
+        <v>-0.747166708067819</v>
       </c>
     </row>
     <row r="326">
@@ -4592,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.317889386581626</v>
+        <v>-0.285994351231548</v>
       </c>
     </row>
     <row r="328">
@@ -4603,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>0.487164055663592</v>
+        <v>-0.887340837748528</v>
       </c>
     </row>
     <row r="329">
@@ -4614,7 +4617,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.977300741140274</v>
+        <v>-1.70017551251519</v>
       </c>
     </row>
     <row r="330">
@@ -4625,7 +4628,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.229250851279451</v>
+        <v>-0.170185847912451</v>
       </c>
     </row>
     <row r="331">
@@ -4636,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.65806720502285</v>
+        <v>-0.908634755739128</v>
       </c>
     </row>
     <row r="332">
@@ -4647,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-1.01044601523151</v>
+        <v>-0.964573578306472</v>
       </c>
     </row>
     <row r="333">
@@ -4658,7 +4661,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.648426067185034</v>
       </c>
     </row>
     <row r="334">
@@ -4669,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.307853246895499</v>
       </c>
     </row>
     <row r="335">
@@ -4680,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.297248728856834</v>
+        <v>-0.120323438837364</v>
       </c>
     </row>
     <row r="336">
@@ -4691,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.235543378653082</v>
+        <v>-0.677404890394852</v>
       </c>
     </row>
     <row r="337">
@@ -4702,7 +4705,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.47757109585125</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="338">
@@ -4713,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>0.584559867459455</v>
+        <v>-0.219668488281974</v>
       </c>
     </row>
     <row r="339">
@@ -4724,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.456668451100119</v>
+        <v>-1.10794738711834</v>
       </c>
     </row>
     <row r="340">
@@ -4735,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.185252528006426</v>
+        <v>-0.230017620508887</v>
       </c>
     </row>
     <row r="341">
@@ -4746,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.254181518168638</v>
       </c>
     </row>
     <row r="342">
@@ -4757,7 +4760,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.443638753062095</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="343">
@@ -4768,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.307100915792957</v>
+        <v>-0.530062957750656</v>
       </c>
     </row>
     <row r="344">
@@ -4779,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>0.223335185665553</v>
+        <v>0.30287150657163</v>
       </c>
     </row>
     <row r="345">
@@ -4790,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.231163271886121</v>
+        <v>-0.581531325415547</v>
       </c>
     </row>
     <row r="346">
@@ -4823,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.60600354534456</v>
       </c>
     </row>
     <row r="349">
@@ -4834,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.120704525844152</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="350">
@@ -4867,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.0144425079220034</v>
+        <v>-0.0191948240410975</v>
       </c>
     </row>
     <row r="353">
@@ -4878,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.188287071594832</v>
+        <v>-0.427402765372915</v>
       </c>
     </row>
     <row r="354">
@@ -4889,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.150245496534369</v>
+        <v>-0.870798150960836</v>
       </c>
     </row>
     <row r="355">
@@ -4911,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>0.621444468356656</v>
+        <v>0.109271587764429</v>
       </c>
     </row>
     <row r="357">
@@ -4922,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.470263766063933</v>
+        <v>-1.2811335792106</v>
       </c>
     </row>
     <row r="358">
@@ -4933,7 +4936,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.962934632197479</v>
+        <v>-0.328408454412138</v>
       </c>
     </row>
     <row r="359">
@@ -4944,7 +4947,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.0849171022319026</v>
+        <v>-0.0769781466456803</v>
       </c>
     </row>
     <row r="360">
@@ -4966,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.179435403228775</v>
+        <v>-0.372962071850668</v>
       </c>
     </row>
     <row r="362">
@@ -4977,7 +4980,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.273219442515984</v>
+        <v>-0.369232109600064</v>
       </c>
     </row>
     <row r="363">
@@ -4988,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.698193440491601</v>
+        <v>-1.24799650103256</v>
       </c>
     </row>
     <row r="364">
@@ -4999,7 +5002,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.01743139528356</v>
       </c>
     </row>
     <row r="365">
@@ -5010,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.242031541322559</v>
+        <v>-0.616710090959756</v>
       </c>
     </row>
     <row r="366">
@@ -5021,7 +5024,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.780756787222489</v>
       </c>
     </row>
     <row r="367">
@@ -5032,7 +5035,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.124083389286745</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="368">
@@ -5043,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.20498468676215</v>
       </c>
     </row>
     <row r="369">
@@ -5054,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.420414939787838</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="370">
@@ -5065,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.520768832842924</v>
+        <v>-0.48891054944271</v>
       </c>
     </row>
     <row r="371">
@@ -5076,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.600173787442811</v>
+        <v>-0.551586252398851</v>
       </c>
     </row>
     <row r="372">
@@ -5098,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.2685128575337</v>
       </c>
     </row>
     <row r="374">
@@ -5109,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.254380537227067</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="375">
@@ -5120,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.388318908296043</v>
+        <v>-0.188266656795464</v>
       </c>
     </row>
     <row r="376">
@@ -5131,7 +5134,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.49376469209985</v>
+        <v>-0.655099042560082</v>
       </c>
     </row>
     <row r="377">
@@ -5153,7 +5156,7 @@
         <v>16</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.663868572361648</v>
+        <v>-0.909466494528284</v>
       </c>
     </row>
     <row r="379">
@@ -5164,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.198223293663807</v>
+        <v>-0.235448171623646</v>
       </c>
     </row>
     <row r="380">
@@ -5175,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>0.167290157944049</v>
+        <v>-0.338487501509591</v>
       </c>
     </row>
     <row r="381">
@@ -5197,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.152770035834398</v>
+        <v>-0.240145566861806</v>
       </c>
     </row>
     <row r="383">
@@ -5208,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.195087467671522</v>
       </c>
     </row>
     <row r="384">
@@ -5230,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.764847325146929</v>
+        <v>-0.324533048361705</v>
       </c>
     </row>
     <row r="386">
@@ -5241,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.486411445017507</v>
+        <v>-0.506229709828966</v>
       </c>
     </row>
     <row r="387">
@@ -5274,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.443435023484682</v>
+        <v>-0.843141324356855</v>
       </c>
     </row>
     <row r="390">
@@ -5285,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-1.79210648223529</v>
+        <v>-1.39121085668576</v>
       </c>
     </row>
     <row r="391">
@@ -5296,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.727566427639854</v>
+        <v>-0.410798521833379</v>
       </c>
     </row>
     <row r="392">
@@ -5307,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.99602370972186</v>
       </c>
     </row>
     <row r="393">
@@ -5318,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.323371789898499</v>
+        <v>-0.173531877133813</v>
       </c>
     </row>
     <row r="394">
@@ -5329,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-3.4931540679445</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="395">
@@ -5340,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>0.602253182701299</v>
+        <v>0.566981426928897</v>
       </c>
     </row>
     <row r="396">
@@ -5351,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-1.23714495079646</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="397">
@@ -5362,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>0.173035165784271</v>
+        <v>-0.381237061252835</v>
       </c>
     </row>
     <row r="398">
@@ -5406,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>0.000822269585627478</v>
+        <v>-0.187629452255096</v>
       </c>
     </row>
     <row r="402">
@@ -5439,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.723251510375746</v>
+        <v>-0.592909840712638</v>
       </c>
     </row>
     <row r="405">
@@ -5450,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.188755953148227</v>
+        <v>-0.17323182453042</v>
       </c>
     </row>
     <row r="406">
@@ -5461,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>0.0655753237318571</v>
+        <v>0.152673447955854</v>
       </c>
     </row>
     <row r="407">
@@ -5472,7 +5475,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.469639423974201</v>
+        <v>-0.415787375057894</v>
       </c>
     </row>
     <row r="408">
@@ -5483,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.278650472026414</v>
+        <v>-0.29801889539214</v>
       </c>
     </row>
     <row r="409">
@@ -5494,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.348607622074653</v>
+        <v>-1.01426082718815</v>
       </c>
     </row>
     <row r="410">
@@ -5505,7 +5508,7 @@
         <v>16</v>
       </c>
       <c r="C410" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.41667582330088</v>
       </c>
     </row>
     <row r="411">
@@ -5516,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.501655545266184</v>
+        <v>-1.92648386578595</v>
       </c>
     </row>
     <row r="412">
@@ -5527,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.305843197093742</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="413">
@@ -5538,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.718278132195605</v>
       </c>
     </row>
     <row r="414">
@@ -5549,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-2.28546270955368</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="415">
@@ -5560,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.216036536254431</v>
       </c>
     </row>
     <row r="416">
@@ -5571,7 +5574,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-1.15092234434177</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="417">
@@ -5582,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-1.80072229778811</v>
+        <v>-3.1702600853954</v>
       </c>
     </row>
     <row r="418">
@@ -5604,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-1.09048982857646</v>
+        <v>-2.07565149111983</v>
       </c>
     </row>
     <row r="420">
@@ -5615,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.322319245228056</v>
+        <v>-2.08852192703096</v>
       </c>
     </row>
     <row r="421">
@@ -5648,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.380153490728618</v>
       </c>
     </row>
     <row r="424">
@@ -5659,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.27815606233816</v>
       </c>
     </row>
     <row r="425">
@@ -5670,7 +5673,7 @@
         <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>-0.605159823274483</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="426">
@@ -5681,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.918282017536179</v>
+        <v>-0.133262695946893</v>
       </c>
     </row>
     <row r="427">
@@ -5703,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.223273819588942</v>
       </c>
     </row>
     <row r="429">
@@ -5714,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.552537110309632</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="430">
@@ -5736,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.798582230059559</v>
       </c>
     </row>
     <row r="432">
@@ -5747,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.331481336519365</v>
+        <v>-0.236842491416583</v>
       </c>
     </row>
     <row r="433">
@@ -5769,7 +5772,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.0811409244343704</v>
+        <v>-0.0269114490677653</v>
       </c>
     </row>
     <row r="435">
@@ -5791,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.184100214314823</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="437">
@@ -5802,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-1.98331611022871</v>
+        <v>-0.502287255152309</v>
       </c>
     </row>
     <row r="438">
@@ -5813,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-1.98281319828367</v>
+        <v>-0.343936194615096</v>
       </c>
     </row>
     <row r="439">
@@ -5824,7 +5827,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.208650640865407</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="440">
@@ -5835,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-1.07113598184452</v>
+        <v>-0.846194818047139</v>
       </c>
     </row>
     <row r="441">
@@ -5846,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.224073442164387</v>
+        <v>-0.176681267072037</v>
       </c>
     </row>
     <row r="442">
@@ -5857,7 +5860,7 @@
         <v>16</v>
       </c>
       <c r="C442" t="n">
-        <v>-0.500704374967733</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="443">
@@ -5868,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.480594448293778</v>
+        <v>-0.264830938833837</v>
       </c>
     </row>
     <row r="444">
@@ -5890,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.596004402268295</v>
       </c>
     </row>
     <row r="446">
@@ -5901,7 +5904,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.665997192889353</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="447">
@@ -5912,7 +5915,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.387079799160347</v>
+        <v>-1.04276093069856</v>
       </c>
     </row>
     <row r="448">
@@ -5923,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.097366261314642</v>
+        <v>-0.250363393251855</v>
       </c>
     </row>
     <row r="449">
@@ -5934,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.42584727007931</v>
+        <v>-0.762629119003351</v>
       </c>
     </row>
     <row r="450">
@@ -5956,7 +5959,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.280735087086727</v>
+        <v>-1.7866898332363</v>
       </c>
     </row>
     <row r="452">
@@ -5967,7 +5970,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.311083779982082</v>
+        <v>-0.476639363526303</v>
       </c>
     </row>
     <row r="453">
@@ -5978,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.24845589508075</v>
+        <v>-0.35563531582559</v>
       </c>
     </row>
     <row r="454">
@@ -5989,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.0903215846497056</v>
+        <v>-0.135402445641385</v>
       </c>
     </row>
     <row r="455">
@@ -6000,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.418117931490123</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="456">
@@ -6011,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.77599123686691</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="457">
@@ -6022,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>-0.174404418413183</v>
+        <v>-0.360387938755984</v>
       </c>
     </row>
     <row r="458">
@@ -6055,7 +6058,7 @@
         <v>16</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.416218129000228</v>
       </c>
     </row>
     <row r="461">
@@ -6077,7 +6080,7 @@
         <v>16</v>
       </c>
       <c r="C462" t="n">
-        <v>-0.482434074983533</v>
+        <v>-0.519745590656818</v>
       </c>
     </row>
     <row r="463">
@@ -6088,7 +6091,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.655810282888378</v>
+        <v>-0.672665612952519</v>
       </c>
     </row>
     <row r="464">
@@ -6099,7 +6102,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.364058062560554</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="465">
@@ -6110,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.158619861407316</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="466">
@@ -6121,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.235094597532274</v>
+        <v>-0.168366543093208</v>
       </c>
     </row>
     <row r="467">
@@ -6132,7 +6135,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.15619582218876</v>
       </c>
     </row>
     <row r="468">
@@ -6143,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.251368606284703</v>
+        <v>-0.213102576512708</v>
       </c>
     </row>
     <row r="469">
@@ -6154,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>0.0980020144690071</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="470">
@@ -6165,7 +6168,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.0509094241165815</v>
+        <v>-0.58347035257725</v>
       </c>
     </row>
     <row r="471">
@@ -6176,7 +6179,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.1854514256944</v>
       </c>
     </row>
     <row r="472">
@@ -6198,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.300312125920361</v>
+        <v>-0.980349873056099</v>
       </c>
     </row>
     <row r="474">
@@ -6209,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>0.0445372493407821</v>
+        <v>-0.223290268108642</v>
       </c>
     </row>
     <row r="475">
@@ -6220,7 +6223,7 @@
         <v>16</v>
       </c>
       <c r="C475" t="n">
-        <v>-0.236114286803768</v>
+        <v>-0.0123139117632056</v>
       </c>
     </row>
     <row r="476">
@@ -6242,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.781274101995596</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="478">
@@ -6253,7 +6256,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-3.67886390389939</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="479">
@@ -6264,7 +6267,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.181000338797787</v>
+        <v>-0.487355388800264</v>
       </c>
     </row>
     <row r="480">
@@ -6286,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>0.432268231524957</v>
+        <v>0.0509546842793206</v>
       </c>
     </row>
     <row r="482">
@@ -6297,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.327559657660494</v>
+        <v>0.732120073913958</v>
       </c>
     </row>
     <row r="483">
@@ -6330,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-1.16296861661194</v>
+        <v>-0.38441633995897</v>
       </c>
     </row>
     <row r="486">
@@ -6341,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.138414817608548</v>
+        <v>0.181277313126245</v>
       </c>
     </row>
     <row r="487">
@@ -6352,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.856361080779716</v>
+        <v>-0.115572490110781</v>
       </c>
     </row>
     <row r="488">
@@ -6363,7 +6366,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.414397709562413</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="489">
@@ -6374,7 +6377,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>0.0700611017212045</v>
+        <v>-0.456011713147423</v>
       </c>
     </row>
     <row r="490">
@@ -6385,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.128627643921088</v>
+        <v>-0.0240610819482261</v>
       </c>
     </row>
     <row r="491">
@@ -6396,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>-0.908047912568569</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="492">
@@ -6418,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.15388453737067</v>
+        <v>-0.214416701394381</v>
       </c>
     </row>
     <row r="494">
@@ -6440,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.656816470489453</v>
+        <v>-0.374705572917239</v>
       </c>
     </row>
     <row r="496">
@@ -6451,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.614493965553808</v>
+        <v>0.15713993042369</v>
       </c>
     </row>
     <row r="497">
@@ -6462,7 +6465,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-1.00999504407005</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="498">
@@ -6473,7 +6476,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.166252176473994</v>
+        <v>-0.161268978528848</v>
       </c>
     </row>
     <row r="499">
@@ -6484,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>0.12995894704871</v>
+        <v>-0.32483626884575</v>
       </c>
     </row>
     <row r="500">
@@ -6495,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>0.296811011155168</v>
+        <v>0.192993839398342</v>
       </c>
     </row>
     <row r="501">
@@ -6539,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.350283090428599</v>
+        <v>-1.56315784226898</v>
       </c>
     </row>
     <row r="505">
@@ -6550,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.505947892498848</v>
+        <v>-0.24953138736386</v>
       </c>
     </row>
     <row r="506">
@@ -6561,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.634497964921765</v>
       </c>
     </row>
     <row r="507">
@@ -6594,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.401226239440899</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="510">
@@ -6627,7 +6630,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.781233599115654</v>
+        <v>-0.2556052813529</v>
       </c>
     </row>
     <row r="513">
@@ -6638,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.229408987688579</v>
+        <v>-0.427098146555594</v>
       </c>
     </row>
     <row r="514">
@@ -6649,7 +6652,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-1.27885212740674</v>
+        <v>-0.596044421984737</v>
       </c>
     </row>
     <row r="515">
@@ -6660,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.465664672566279</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="516">
@@ -6671,7 +6674,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-1.84918248843261</v>
+        <v>-0.185099560826369</v>
       </c>
     </row>
     <row r="517">
@@ -6682,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.391780610579788</v>
+        <v>-0.343624541341097</v>
       </c>
     </row>
     <row r="518">
@@ -6693,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-1.74719420521207</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="519">
@@ -6704,7 +6707,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.522713088088457</v>
+        <v>-2.13636968494802</v>
       </c>
     </row>
     <row r="520">
@@ -6715,7 +6718,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.440960411216135</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="521">
@@ -6726,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.212853293032194</v>
+        <v>-0.208781210596357</v>
       </c>
     </row>
     <row r="522">
@@ -6737,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.477606647444813</v>
       </c>
     </row>
     <row r="523">
@@ -6748,7 +6751,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.207015369261301</v>
       </c>
     </row>
     <row r="524">
@@ -6759,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>0.486871989031738</v>
+        <v>-0.809250133880338</v>
       </c>
     </row>
     <row r="525">
@@ -6792,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.265528688835173</v>
+        <v>-1.01811973316643</v>
       </c>
     </row>
     <row r="528">
@@ -6803,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>0.376036712189596</v>
+        <v>-0.556981873287943</v>
       </c>
     </row>
     <row r="529">
@@ -6814,7 +6817,7 @@
         <v>16</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.457235167182641</v>
       </c>
     </row>
     <row r="530">
@@ -6825,7 +6828,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.172323360635391</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="531">
@@ -6836,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-1.35398057932771</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="532">
@@ -6847,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.552590872184571</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="533">
@@ -6858,7 +6861,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.0631013828245846</v>
       </c>
     </row>
     <row r="534">
@@ -6880,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.21426013923664</v>
+        <v>0.177291493901881</v>
       </c>
     </row>
     <row r="536">
@@ -6891,7 +6894,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.102805815888714</v>
+        <v>-0.616300894603566</v>
       </c>
     </row>
     <row r="537">
@@ -6902,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.46731969301144</v>
+        <v>-2.45903377735982</v>
       </c>
     </row>
     <row r="538">
@@ -6913,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>0.17368940696595</v>
+        <v>-0.414404856595562</v>
       </c>
     </row>
     <row r="539">
@@ -6924,7 +6927,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>0.212337378054379</v>
+        <v>-1.07342512253101</v>
       </c>
     </row>
     <row r="540">
@@ -6935,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.338591212084359</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="541">
@@ -6946,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.23370419539555</v>
+        <v>-0.316287577523531</v>
       </c>
     </row>
     <row r="542">
@@ -6968,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.252019260024379</v>
+        <v>-0.612476117008212</v>
       </c>
     </row>
     <row r="544">
@@ -6979,7 +6982,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>0.335923897522634</v>
+        <v>0.384618186006306</v>
       </c>
     </row>
     <row r="545">
@@ -6990,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.280820766473017</v>
+        <v>-0.274767723121726</v>
       </c>
     </row>
     <row r="546">
@@ -7001,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.240729599281691</v>
+        <v>-4.29331728434149</v>
       </c>
     </row>
     <row r="547">
@@ -7012,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.308242650201968</v>
       </c>
     </row>
     <row r="548">
@@ -7034,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.235119652280339</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="550">
@@ -7045,7 +7048,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.828783245554588</v>
+        <v>-0.292180867773473</v>
       </c>
     </row>
     <row r="551">
@@ -7056,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.02258868961391</v>
       </c>
     </row>
     <row r="552">
@@ -7067,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.138756816273518</v>
+        <v>-0.114575304693714</v>
       </c>
     </row>
     <row r="553">
@@ -7078,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.409916013759898</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="554">
@@ -7100,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.288262537357946</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="556">
@@ -7111,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>0.447764223235746</v>
+        <v>0.255483441431159</v>
       </c>
     </row>
     <row r="557">
@@ -7122,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.198444814661229</v>
+        <v>-1.13566835762391</v>
       </c>
     </row>
     <row r="558">
@@ -7133,7 +7136,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.101741868834975</v>
+        <v>-0.408261559900981</v>
       </c>
     </row>
     <row r="559">
@@ -7144,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.130372267526052</v>
+        <v>-0.24750100357202</v>
       </c>
     </row>
     <row r="560">
@@ -7166,7 +7169,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.516072606677755</v>
+        <v>-0.185118830009111</v>
       </c>
     </row>
     <row r="562">
@@ -7177,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.36053449141265</v>
       </c>
     </row>
     <row r="563">
@@ -7188,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.707899590330096</v>
+        <v>-0.840477164103219</v>
       </c>
     </row>
     <row r="564">
@@ -7210,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.288582968416294</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="566">
@@ -7221,7 +7224,7 @@
         <v>16</v>
       </c>
       <c r="C566" t="n">
-        <v>-1.48064235338233</v>
+        <v>-0.620850427407033</v>
       </c>
     </row>
     <row r="567">
@@ -7232,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-1.52791611272156</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7243,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.178181817978</v>
+        <v>-4.34559549941711</v>
       </c>
     </row>
     <row r="569">
@@ -7254,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.0802200829119664</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="570">
@@ -7265,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.637290090919723</v>
+        <v>-0.857702639644483</v>
       </c>
     </row>
     <row r="571">
@@ -7276,7 +7279,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.410983319396477</v>
+        <v>-0.374867064481552</v>
       </c>
     </row>
     <row r="572">
@@ -7298,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.206872333973631</v>
       </c>
     </row>
     <row r="574">
@@ -7309,7 +7312,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.272189248108282</v>
+        <v>-0.248081902084056</v>
       </c>
     </row>
     <row r="575">
@@ -7320,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.415508244337671</v>
+        <v>-0.332444146465001</v>
       </c>
     </row>
     <row r="576">
@@ -7331,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.0226289801286736</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="577">
@@ -7353,7 +7356,7 @@
         <v>16</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.275655402644096</v>
+        <v>-0.532393694799484</v>
       </c>
     </row>
     <row r="579">
@@ -7364,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.891109818806114</v>
+        <v>-1.26325059977305</v>
       </c>
     </row>
     <row r="580">
@@ -7375,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.0134555843954174</v>
+        <v>0.298614979648977</v>
       </c>
     </row>
     <row r="581">
@@ -7386,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.147959183673469</v>
+        <v>-8.68717466189029</v>
       </c>
     </row>
     <row r="582">
@@ -7397,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.35879462610831</v>
+        <v>-0.37016937340659</v>
       </c>
     </row>
     <row r="583">
@@ -7419,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.556167877901516</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="585">
@@ -7430,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.314694269138269</v>
+        <v>-0.16522472087636</v>
       </c>
     </row>
     <row r="586">
@@ -7441,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.637262111052434</v>
+        <v>-0.212222739873956</v>
       </c>
     </row>
     <row r="587">
@@ -7452,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.9326724595964</v>
+        <v>-0.35790317940187</v>
       </c>
     </row>
     <row r="588">
@@ -7463,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.03185892903986</v>
       </c>
     </row>
     <row r="589">
@@ -7474,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.307719496874774</v>
+        <v>-0.386517851385029</v>
       </c>
     </row>
     <row r="590">
@@ -7485,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-3.72419837513529</v>
+        <v>-0.634683527929235</v>
       </c>
     </row>
     <row r="591">
@@ -7496,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.14795918367347</v>
+        <v>0.0904993228999469</v>
       </c>
     </row>
     <row r="592">
@@ -7518,7 +7521,7 @@
         <v>16</v>
       </c>
       <c r="C593" t="n">
-        <v>-1.38344798620699</v>
+        <v>-0.162256050133672</v>
       </c>
     </row>
     <row r="594">
@@ -7529,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-5.57101832048051</v>
+        <v>-1.2481984952462</v>
       </c>
     </row>
     <row r="595">
@@ -7540,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>0.569791895958432</v>
+        <v>0.10961611706206</v>
       </c>
     </row>
     <row r="596">
@@ -7551,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-1.12503766738166</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="597">
@@ -7562,7 +7565,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.250985059794095</v>
+        <v>-0.313957830871075</v>
       </c>
     </row>
     <row r="598">
@@ -7573,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.32778645330932</v>
+        <v>-0.0383008964902365</v>
       </c>
     </row>
     <row r="599">
@@ -7584,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-1.12322593847964</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="600">
@@ -7606,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.0215173364363985</v>
+        <v>-0.922894343032088</v>
       </c>
     </row>
     <row r="602">
@@ -7650,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.158580773759844</v>
+        <v>-0.533753774972465</v>
       </c>
     </row>
     <row r="606">
@@ -7672,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.17919678757967</v>
+        <v>-0.1742995277104</v>
       </c>
     </row>
     <row r="608">
@@ -7683,7 +7686,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-1.10260541771082</v>
+        <v>-0.977733841905691</v>
       </c>
     </row>
     <row r="609">
@@ -7705,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.384551531895357</v>
+        <v>-0.22147882590503</v>
       </c>
     </row>
     <row r="611">
@@ -7716,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-1.61657668745063</v>
+        <v>-0.443122936027087</v>
       </c>
     </row>
     <row r="612">
@@ -7727,7 +7730,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-1.52658263364276</v>
+        <v>-0.892418684974207</v>
       </c>
     </row>
     <row r="613">
@@ -7738,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.233936070092583</v>
+        <v>-1.68485292343655</v>
       </c>
     </row>
     <row r="614">
@@ -7749,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.17458768918583</v>
       </c>
     </row>
     <row r="615">
@@ -7760,7 +7763,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.199577035226726</v>
+        <v>0.0876589012224113</v>
       </c>
     </row>
     <row r="616">
@@ -7771,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.91964210795632</v>
+        <v>-1.88131562797421</v>
       </c>
     </row>
     <row r="617">
@@ -7782,7 +7785,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.41009132112559</v>
       </c>
     </row>
     <row r="618">
@@ -7793,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-1.68232083025642</v>
+        <v>-0.122947258492318</v>
       </c>
     </row>
     <row r="619">
@@ -7804,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.279326563659017</v>
+        <v>-0.223295084626262</v>
       </c>
     </row>
     <row r="620">
@@ -7815,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.606230110334967</v>
       </c>
     </row>
     <row r="621">
@@ -7826,7 +7829,7 @@
         <v>16</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.84210883528786</v>
       </c>
     </row>
     <row r="622">
@@ -7837,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-4.60304036001176</v>
+        <v>-0.395825758072845</v>
       </c>
     </row>
     <row r="623">
@@ -7848,7 +7851,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>0.0126686914663434</v>
+        <v>-0.50831893113154</v>
       </c>
     </row>
     <row r="624">
@@ -7859,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>0.153859048265431</v>
+        <v>-1.15709502550892</v>
       </c>
     </row>
     <row r="625">
@@ -7881,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.160329509331934</v>
+        <v>-0.244704961710929</v>
       </c>
     </row>
     <row r="627">
@@ -7892,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.790978305932219</v>
       </c>
     </row>
     <row r="628">
@@ -7914,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>0.165616538992752</v>
+        <v>-1.97864681374573</v>
       </c>
     </row>
     <row r="630">
@@ -7925,7 +7928,7 @@
         <v>16</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.198380983918229</v>
+        <v>-0.925699922660729</v>
       </c>
     </row>
     <row r="631">
@@ -7936,7 +7939,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.466612554072543</v>
       </c>
     </row>
     <row r="632">
@@ -7947,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.162726230802148</v>
+        <v>-0.195266883555933</v>
       </c>
     </row>
     <row r="633">
@@ -7958,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.207865844721441</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="634">
@@ -7969,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.244098534521669</v>
+        <v>-0.19475384709117</v>
       </c>
     </row>
     <row r="635">
@@ -7980,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.25554937402366</v>
+        <v>-3.76112313664875</v>
       </c>
     </row>
     <row r="636">
@@ -7991,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>0.092359817855708</v>
+        <v>0.150937983094838</v>
       </c>
     </row>
     <row r="637">
@@ -8002,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.230724354030502</v>
+        <v>-0.221422911199897</v>
       </c>
     </row>
     <row r="638">
@@ -8024,7 +8027,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.544002882382311</v>
+        <v>-0.0105823340973377</v>
       </c>
     </row>
     <row r="640">
@@ -8035,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.583403703548845</v>
+        <v>-0.380505048681627</v>
       </c>
     </row>
     <row r="641">
@@ -8046,7 +8049,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.177984415819533</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="642">
@@ -8057,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.66307777718573</v>
       </c>
     </row>
     <row r="643">
@@ -8068,7 +8071,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.39248869788038</v>
       </c>
     </row>
     <row r="644">
@@ -8079,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.355257214298183</v>
+        <v>-0.520600786374571</v>
       </c>
     </row>
     <row r="645">
@@ -8090,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.565433196601179</v>
+        <v>-0.198163909454477</v>
       </c>
     </row>
     <row r="646">
@@ -8101,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.153995898679584</v>
+        <v>-0.22236243796597</v>
       </c>
     </row>
     <row r="647">
@@ -8112,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>0.45229662411727</v>
+        <v>-0.00162329358037527</v>
       </c>
     </row>
     <row r="648">
@@ -8123,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>0.729882657308348</v>
+        <v>0.513496188669475</v>
       </c>
     </row>
     <row r="649">
@@ -8145,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>0.424047862592854</v>
+        <v>0.387165063024908</v>
       </c>
     </row>
     <row r="651">
@@ -8156,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.554234735676563</v>
+        <v>-0.209555226429982</v>
       </c>
     </row>
     <row r="652">
@@ -8167,7 +8170,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.198731280246697</v>
+        <v>-0.343628260320187</v>
       </c>
     </row>
     <row r="653">
@@ -8178,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.577402006408252</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8189,7 +8192,7 @@
         <v>16</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.645864520625844</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="655">
@@ -8200,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.525696628374297</v>
+        <v>-1.84849190090945</v>
       </c>
     </row>
     <row r="656">
@@ -8211,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.0865660667707797</v>
       </c>
     </row>
     <row r="657">
@@ -8233,7 +8236,7 @@
         <v>16</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.336032264347645</v>
       </c>
     </row>
     <row r="659">
@@ -8266,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.876592645247015</v>
+        <v>-0.298464089976665</v>
       </c>
     </row>
     <row r="662">
@@ -8277,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.163083654746311</v>
+        <v>-0.345248750909442</v>
       </c>
     </row>
     <row r="663">
@@ -8299,7 +8302,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.4980553682583</v>
+        <v>-0.215907570578147</v>
       </c>
     </row>
     <row r="665">
@@ -8310,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.00234003093537338</v>
+        <v>-0.332108095485128</v>
       </c>
     </row>
     <row r="666">
@@ -8321,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-1.43972311951377</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="667">
@@ -8332,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.202917649484913</v>
+        <v>-1.95696816190651</v>
       </c>
     </row>
     <row r="668">
@@ -8354,7 +8357,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.36629551513797</v>
       </c>
     </row>
     <row r="670">
@@ -8387,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.197318216516583</v>
+        <v>-0.322121522635919</v>
       </c>
     </row>
     <row r="673">
@@ -8398,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-2.37612713171231</v>
+        <v>-0.684442981306579</v>
       </c>
     </row>
     <row r="674">
@@ -8409,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.416539851356992</v>
+        <v>-8.64993909652213</v>
       </c>
     </row>
     <row r="675">
@@ -8420,7 +8423,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.144090813314969</v>
+        <v>-1.00019132694277</v>
       </c>
     </row>
     <row r="676">
@@ -8431,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.54074813862283</v>
       </c>
     </row>
     <row r="677">
@@ -8453,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.35058849634301</v>
       </c>
     </row>
     <row r="679">
@@ -8464,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.705882493712382</v>
+        <v>-0.175099666564629</v>
       </c>
     </row>
     <row r="680">
@@ -8486,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.398900455404622</v>
+        <v>-0.24727288687293</v>
       </c>
     </row>
     <row r="682">
@@ -8508,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.880296119378348</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="684">
@@ -8530,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>0.32988542826797</v>
+        <v>0.395825675825481</v>
       </c>
     </row>
     <row r="686">
@@ -8541,7 +8544,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.26406061642254</v>
       </c>
     </row>
     <row r="687">
@@ -8563,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.25838134501588</v>
+        <v>-1.19937701231971</v>
       </c>
     </row>
     <row r="689">
@@ -8596,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.930989798552731</v>
+        <v>-1.45425074222448</v>
       </c>
     </row>
     <row r="692">
@@ -8607,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-2.7001539801297</v>
+        <v>-1.82377244989894</v>
       </c>
     </row>
     <row r="693">
@@ -8618,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-1.53889333050545</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="694">
@@ -8629,7 +8632,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>0.417902259906604</v>
+        <v>-0.0449210572519312</v>
       </c>
     </row>
     <row r="695">
@@ -8640,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.135917465770847</v>
       </c>
     </row>
     <row r="696">
@@ -8673,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.654147332715525</v>
+        <v>-0.250552210463826</v>
       </c>
     </row>
     <row r="699">
@@ -8684,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-1.63290107314809</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="700">
@@ -8695,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.212839861858254</v>
+        <v>-0.38343723943456</v>
       </c>
     </row>
     <row r="701">
@@ -8706,7 +8709,7 @@
         <v>16</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.766769092074197</v>
+        <v>-1.0008092043053</v>
       </c>
     </row>
     <row r="702">
@@ -8728,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.337211922658502</v>
       </c>
     </row>
     <row r="704">
@@ -8750,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.418048840546432</v>
       </c>
     </row>
     <row r="706">
@@ -8761,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-1.16128308173192</v>
+        <v>-0.100445135576177</v>
       </c>
     </row>
     <row r="707">
@@ -8772,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.2767469661587</v>
+        <v>-0.886478172177583</v>
       </c>
     </row>
     <row r="708">
@@ -8783,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.97818902882898</v>
+        <v>-2.84242382221794</v>
       </c>
     </row>
     <row r="709">
@@ -8805,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.255373652805069</v>
+        <v>-0.222085731724911</v>
       </c>
     </row>
     <row r="711">
@@ -8816,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.788276497710797</v>
       </c>
     </row>
     <row r="712">
@@ -8827,7 +8830,7 @@
         <v>16</v>
       </c>
       <c r="C712" t="n">
-        <v>-1.64902658103996</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="713">
@@ -8849,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.263726842374536</v>
+        <v>-0.629961892655869</v>
       </c>
     </row>
     <row r="715">
@@ -8871,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.12009942235953</v>
       </c>
     </row>
     <row r="717">
@@ -8882,7 +8885,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.21521810706622</v>
       </c>
     </row>
     <row r="718">
@@ -8893,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.856318125951787</v>
+        <v>-0.383573366717618</v>
       </c>
     </row>
     <row r="719">
@@ -8904,7 +8907,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>0.177500795748636</v>
+        <v>-1.30231693435017</v>
       </c>
     </row>
     <row r="720">
@@ -8926,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>0.0394823399998476</v>
+        <v>-0.0664091833421332</v>
       </c>
     </row>
     <row r="722">
@@ -8937,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.706486395038038</v>
+        <v>-1.00052953155399</v>
       </c>
     </row>
     <row r="723">
@@ -8948,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.533447125971263</v>
+        <v>-0.398665204431731</v>
       </c>
     </row>
     <row r="724">
@@ -8959,7 +8962,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-1.37644193328327</v>
+        <v>-0.220878144160826</v>
       </c>
     </row>
     <row r="725">
@@ -8970,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.173465467750622</v>
+        <v>-0.15852355096442</v>
       </c>
     </row>
     <row r="726">
@@ -8992,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.531798020365757</v>
+        <v>-0.410962436334683</v>
       </c>
     </row>
     <row r="728">
@@ -9003,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.176207694328508</v>
+        <v>-0.378073038417469</v>
       </c>
     </row>
     <row r="729">
@@ -9014,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>0.234999729500062</v>
+        <v>-0.246587099703433</v>
       </c>
     </row>
     <row r="730">
@@ -9025,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.0403008222102581</v>
+        <v>0.172073858227314</v>
       </c>
     </row>
     <row r="731">
@@ -9036,7 +9039,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.659233694855072</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="732">
@@ -9047,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.420606870459235</v>
+        <v>0.728143206565821</v>
       </c>
     </row>
     <row r="733">
@@ -9058,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.778344252652334</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="734">
@@ -9080,7 +9083,7 @@
         <v>16</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.725366315305082</v>
+        <v>-0.191053058905267</v>
       </c>
     </row>
     <row r="736">
@@ -9091,7 +9094,7 @@
         <v>16</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.730820644516372</v>
+        <v>-0.262639159598897</v>
       </c>
     </row>
     <row r="737">
@@ -9102,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.212845170837719</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="738">
@@ -9124,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>0.407894354592844</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="740">
@@ -9135,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.157458373371398</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="741">
@@ -9146,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.14934172722161</v>
       </c>
     </row>
     <row r="742">
@@ -9157,7 +9160,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.787452448295442</v>
+        <v>-0.537532988316768</v>
       </c>
     </row>
     <row r="743">
@@ -9179,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-2.66758027436195</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="745">
@@ -9201,7 +9204,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.349467929185124</v>
+        <v>-0.299745699415473</v>
       </c>
     </row>
     <row r="747">
@@ -9212,7 +9215,7 @@
         <v>16</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.462738990021512</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="748">
@@ -9223,7 +9226,7 @@
         <v>16</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.353582287442553</v>
+        <v>-0.0444069938253364</v>
       </c>
     </row>
     <row r="749">
@@ -9234,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.188439211089014</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="750">
@@ -9245,7 +9248,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-1.24596019068733</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="751">
@@ -9256,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-2.32637862972265</v>
+        <v>0.0725842016318078</v>
       </c>
     </row>
     <row r="752">
@@ -9267,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.907307394305209</v>
       </c>
     </row>
     <row r="753">
@@ -9278,7 +9281,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.99904062472869</v>
       </c>
     </row>
     <row r="754">
@@ -9289,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>0.188261607620765</v>
+        <v>-0.0823304375165612</v>
       </c>
     </row>
     <row r="755">
@@ -9300,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.241912119415771</v>
+        <v>-0.191107917153393</v>
       </c>
     </row>
     <row r="756">
@@ -9311,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.718103187047201</v>
+        <v>-0.83608389304514</v>
       </c>
     </row>
     <row r="757">
@@ -9344,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.211145228419664</v>
+        <v>-0.269312759448249</v>
       </c>
     </row>
     <row r="760">
@@ -9355,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.268950787730522</v>
+        <v>-0.238874853018506</v>
       </c>
     </row>
     <row r="761">
@@ -9366,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.61771046105111</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="762">
@@ -9377,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.258305422705114</v>
+        <v>-0.161797928932448</v>
       </c>
     </row>
     <row r="763">
@@ -9388,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.144267643640234</v>
+        <v>-2.22484029879704</v>
       </c>
     </row>
     <row r="764">
@@ -9399,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>0.284590346245451</v>
+        <v>0.200216768109986</v>
       </c>
     </row>
     <row r="765">
@@ -9410,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.111822510361547</v>
+        <v>-0.0141711725725286</v>
       </c>
     </row>
     <row r="766">
@@ -9432,7 +9435,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.380188351131313</v>
       </c>
     </row>
     <row r="768">
@@ -9443,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-1.3078703307207</v>
+        <v>-1.24736391028236</v>
       </c>
     </row>
     <row r="769">
@@ -9454,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.288476334603294</v>
+        <v>-0.272487976878651</v>
       </c>
     </row>
     <row r="770">
@@ -9465,7 +9468,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.18767675413607</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="771">
@@ -9476,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.623350669096146</v>
+        <v>-0.1202982456993</v>
       </c>
     </row>
     <row r="772">
@@ -9487,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.256513124227187</v>
+        <v>-0.1874350700986</v>
       </c>
     </row>
     <row r="773">
@@ -9498,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.400211580104401</v>
       </c>
     </row>
     <row r="774">
@@ -9509,7 +9512,7 @@
         <v>16</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.438724952309768</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="775">
@@ -9531,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.536262355727148</v>
+        <v>-1.92554318336402</v>
       </c>
     </row>
     <row r="777">
@@ -9542,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-1.09809923863181</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="778">
@@ -9553,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.226409774701805</v>
+        <v>-0.344783235327174</v>
       </c>
     </row>
     <row r="779">
@@ -9564,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.441980608348673</v>
+        <v>-0.219926622627981</v>
       </c>
     </row>
     <row r="780">
@@ -9575,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.201253792467047</v>
+        <v>-2.12368386448659</v>
       </c>
     </row>
     <row r="781">
@@ -9597,7 +9600,7 @@
         <v>16</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.23259051544607</v>
+        <v>-0.0137682959880998</v>
       </c>
     </row>
     <row r="783">
@@ -9619,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>0.213248192523769</v>
+        <v>-0.33637876131689</v>
       </c>
     </row>
     <row r="785">
@@ -9641,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-1.19707940363809</v>
+        <v>-1.94869104945641</v>
       </c>
     </row>
     <row r="787">
@@ -9652,7 +9655,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.634296083454196</v>
+        <v>0.00818176420836925</v>
       </c>
     </row>
     <row r="788">
@@ -9674,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.227643040311204</v>
+        <v>-0.264266923626599</v>
       </c>
     </row>
     <row r="790">
@@ -9707,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.279681169248562</v>
+        <v>0.464123440910049</v>
       </c>
     </row>
     <row r="793">
@@ -9718,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.227118524641807</v>
       </c>
     </row>
     <row r="794">
@@ -9740,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.16256908667684</v>
       </c>
     </row>
     <row r="796">
@@ -9751,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.245261579694401</v>
+        <v>-0.647045216319386</v>
       </c>
     </row>
     <row r="797">
@@ -9762,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.293066816698453</v>
+        <v>-0.327464262856209</v>
       </c>
     </row>
     <row r="798">
@@ -9773,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.748463509064626</v>
+        <v>-0.474205691295839</v>
       </c>
     </row>
     <row r="799">
@@ -9784,7 +9787,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.509518678478809</v>
+        <v>-0.284376477215499</v>
       </c>
     </row>
     <row r="800">
@@ -9806,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-2.30618493766574</v>
+        <v>-3.06577797049459</v>
       </c>
     </row>
     <row r="802">
@@ -9817,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.204336551662564</v>
+        <v>-0.445203481833152</v>
       </c>
     </row>
     <row r="803">
@@ -9828,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.245866751117456</v>
       </c>
     </row>
     <row r="804">
@@ -9839,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.267421833482065</v>
+        <v>-0.269191978623712</v>
       </c>
     </row>
     <row r="805">
@@ -9861,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.899395250972941</v>
       </c>
     </row>
     <row r="807">
@@ -9883,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.701788280069297</v>
+        <v>-0.722899282899189</v>
       </c>
     </row>
     <row r="809">
@@ -9894,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>0.270099474800409</v>
+        <v>-0.341936408594388</v>
       </c>
     </row>
     <row r="810">
@@ -9905,7 +9908,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.248577755112897</v>
+        <v>-14.7964423319439</v>
       </c>
     </row>
     <row r="811">
@@ -9916,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.345951773121209</v>
       </c>
     </row>
     <row r="812">
@@ -9927,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.94592064782235</v>
       </c>
     </row>
     <row r="813">
@@ -9949,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.231344342252174</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="815">
@@ -9960,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.225585969215863</v>
+        <v>-0.214334550480237</v>
       </c>
     </row>
     <row r="816">
@@ -9982,7 +9985,7 @@
         <v>16</v>
       </c>
       <c r="C817" t="n">
-        <v>-1.14791012710073</v>
+        <v>-0.599078261326895</v>
       </c>
     </row>
     <row r="818">
@@ -9993,7 +9996,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>0.013300267028417</v>
+        <v>-0.303108801328715</v>
       </c>
     </row>
     <row r="819">
@@ -10004,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.165128375694469</v>
+        <v>-1.37972873596357</v>
       </c>
     </row>
     <row r="820">
@@ -10015,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.370537067327108</v>
+        <v>-0.291100353182632</v>
       </c>
     </row>
     <row r="821">
@@ -10037,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.548618823192144</v>
       </c>
     </row>
     <row r="823">
@@ -10048,7 +10051,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.225480481887318</v>
+        <v>-0.228006828852632</v>
       </c>
     </row>
     <row r="824">
@@ -10059,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.436181964571347</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="825">
@@ -10070,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.621016970987116</v>
+        <v>-2.41636192127537</v>
       </c>
     </row>
     <row r="826">
@@ -10092,7 +10095,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.164241407813684</v>
+        <v>-0.398568900536704</v>
       </c>
     </row>
     <row r="828">
@@ -10103,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.379253971608601</v>
+        <v>-0.369250763444529</v>
       </c>
     </row>
     <row r="829">
@@ -10114,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-1.20336715026576</v>
+        <v>-0.205451435168126</v>
       </c>
     </row>
     <row r="830">
@@ -10125,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-1.61915683796734</v>
+        <v>-0.231779252965021</v>
       </c>
     </row>
     <row r="831">
@@ -10136,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.321112762028357</v>
+        <v>-0.657878809495367</v>
       </c>
     </row>
     <row r="832">
@@ -10158,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.497110189819838</v>
+        <v>-0.410244375419623</v>
       </c>
     </row>
     <row r="834">
@@ -10180,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>0.112563040160767</v>
+        <v>-1.24792774876061</v>
       </c>
     </row>
     <row r="836">
@@ -10191,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.191009211669672</v>
+        <v>-0.262324462910519</v>
       </c>
     </row>
     <row r="837">
@@ -10202,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.568457965269189</v>
+        <v>-0.374538336827938</v>
       </c>
     </row>
     <row r="838">
@@ -10213,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.324877541319908</v>
+        <v>-2.48667931162871</v>
       </c>
     </row>
     <row r="839">
@@ -10224,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.46585934905501</v>
       </c>
     </row>
     <row r="840">
@@ -10235,7 +10238,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.188968589107748</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="841">
@@ -10268,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.152568437196443</v>
+        <v>-2.59156708509078</v>
       </c>
     </row>
     <row r="844">
@@ -10279,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.623908920274636</v>
       </c>
     </row>
     <row r="845">
@@ -10301,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.22479757060539</v>
       </c>
     </row>
     <row r="847">
@@ -10312,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.535189587910194</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="848">
@@ -10334,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.273714746946887</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="850">
@@ -10345,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.304735072344774</v>
+        <v>-0.192076222129928</v>
       </c>
     </row>
     <row r="851">
@@ -10356,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.0521301393272808</v>
+        <v>-0.275457045210009</v>
       </c>
     </row>
     <row r="852">
@@ -10367,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.156517965479831</v>
+        <v>-1.09221568549213</v>
       </c>
     </row>
     <row r="853">
@@ -10389,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-1.08172121157597</v>
+        <v>-0.992973868488089</v>
       </c>
     </row>
     <row r="855">
@@ -10400,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-1.156510384552</v>
+        <v>-0.640386089714468</v>
       </c>
     </row>
     <row r="856">
@@ -10411,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.216020863075845</v>
+        <v>-0.196937870196706</v>
       </c>
     </row>
     <row r="857">
@@ -10422,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.365362134357526</v>
+        <v>-0.260301912135181</v>
       </c>
     </row>
     <row r="858">
@@ -10455,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.478318246981971</v>
+        <v>-3.68465927600866</v>
       </c>
     </row>
     <row r="861">
@@ -10466,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.45068015424953</v>
       </c>
     </row>
     <row r="862">
@@ -10488,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-2.67979186930221</v>
+        <v>-0.432384675766359</v>
       </c>
     </row>
     <row r="864">
@@ -10499,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.718846528596109</v>
       </c>
     </row>
     <row r="865">
@@ -10532,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.457847302168463</v>
+        <v>-0.353712911920524</v>
       </c>
     </row>
     <row r="868">
@@ -10543,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.450290782375808</v>
+        <v>-0.246694007727452</v>
       </c>
     </row>
     <row r="869">
@@ -10554,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.267825892155966</v>
+        <v>-0.239260173535865</v>
       </c>
     </row>
     <row r="870">
@@ -10576,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.69657558089104</v>
+        <v>-0.195187758989134</v>
       </c>
     </row>
     <row r="872">
@@ -10587,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.699662616231458</v>
+        <v>-0.20185801597647</v>
       </c>
     </row>
     <row r="873">
@@ -10609,7 +10612,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.565362291111101</v>
       </c>
     </row>
     <row r="875">
@@ -10620,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.235085384184904</v>
+        <v>-0.626387046850914</v>
       </c>
     </row>
     <row r="876">
@@ -10631,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.334999947014952</v>
+        <v>-0.425663461382886</v>
       </c>
     </row>
     <row r="877">
@@ -10642,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.318145211066814</v>
+        <v>0.0560199878898417</v>
       </c>
     </row>
     <row r="878">
@@ -10653,7 +10656,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.297936820318565</v>
+        <v>-0.530036595781912</v>
       </c>
     </row>
     <row r="879">
@@ -10664,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-1.19874796404866</v>
+        <v>-0.729435594772575</v>
       </c>
     </row>
     <row r="880">
@@ -10675,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.553182319740353</v>
+        <v>-0.39358530039025</v>
       </c>
     </row>
     <row r="881">
@@ -10686,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.205012521704124</v>
+        <v>-2.44051693344292</v>
       </c>
     </row>
     <row r="882">
@@ -10697,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-1.07784362116601</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="883">
@@ -10708,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.335634958316104</v>
       </c>
     </row>
     <row r="884">
@@ -10719,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.207168365086699</v>
+        <v>0.00566143817950671</v>
       </c>
     </row>
     <row r="885">
@@ -10730,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.307636408729952</v>
+        <v>-0.259558158879223</v>
       </c>
     </row>
     <row r="886">
@@ -10741,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.548701357957006</v>
+        <v>-0.176655928177281</v>
       </c>
     </row>
     <row r="887">
@@ -10752,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.419691956719318</v>
+        <v>-0.463785978317588</v>
       </c>
     </row>
     <row r="888">
@@ -10763,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.547079187575652</v>
+        <v>-2.67479043199165</v>
       </c>
     </row>
     <row r="889">
@@ -10774,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.301878421782717</v>
+        <v>-2.01133604827535</v>
       </c>
     </row>
     <row r="890">
@@ -10785,7 +10788,7 @@
         <v>16</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.218384597839274</v>
+        <v>-0.136620992619202</v>
       </c>
     </row>
     <row r="891">
@@ -10796,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.175567901761209</v>
+        <v>-2.47362251878213</v>
       </c>
     </row>
     <row r="892">
@@ -10818,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>0.0535577413110946</v>
+        <v>-0.33801426718521</v>
       </c>
     </row>
     <row r="894">
@@ -10829,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.259796165804512</v>
       </c>
     </row>
     <row r="895">
@@ -10840,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.965464506836668</v>
+        <v>-0.276130203832479</v>
       </c>
     </row>
     <row r="896">
@@ -10851,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>0.457911364451859</v>
+        <v>-0.351011091929642</v>
       </c>
     </row>
     <row r="897">
@@ -10862,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.149543583436194</v>
+        <v>-0.345536170959125</v>
       </c>
     </row>
     <row r="898">
@@ -10873,7 +10876,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.34530429577502</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="899">
@@ -10884,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.252176377003928</v>
+        <v>-0.259089116895747</v>
       </c>
     </row>
     <row r="900">
@@ -10895,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.372597571608846</v>
+        <v>-0.179604458638346</v>
       </c>
     </row>
     <row r="901">
@@ -10917,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.167133624589943</v>
       </c>
     </row>
     <row r="903">
@@ -10928,7 +10931,7 @@
         <v>16</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.232502615163334</v>
       </c>
     </row>
     <row r="904">
@@ -10939,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-1.21397879919004</v>
+        <v>-0.191539631929398</v>
       </c>
     </row>
     <row r="905">
@@ -10950,7 +10953,7 @@
         <v>16</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.0871578504610633</v>
+        <v>-0.165066761473808</v>
       </c>
     </row>
     <row r="906">
@@ -10972,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.583402540697376</v>
+        <v>-0.239559036244151</v>
       </c>
     </row>
     <row r="908">
@@ -10983,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.245147140700965</v>
+        <v>-0.300886098936151</v>
       </c>
     </row>
     <row r="909">
@@ -10994,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.626323020508302</v>
+        <v>-1.72876805813825</v>
       </c>
     </row>
     <row r="910">
@@ -11016,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.737531750278453</v>
+        <v>-1.31131276138267</v>
       </c>
     </row>
     <row r="912">
@@ -11027,7 +11030,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-2.50867748204541</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="913">
@@ -11038,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>0.18566456352881</v>
+        <v>-0.0760804085962463</v>
       </c>
     </row>
     <row r="914">
@@ -11049,7 +11052,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.23554221360307</v>
       </c>
     </row>
     <row r="915">
@@ -11060,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.406452501637975</v>
+        <v>-0.485406526881486</v>
       </c>
     </row>
     <row r="916">
@@ -11071,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-1.28049425277244</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="917">
@@ -11082,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.460180512459925</v>
+        <v>-0.663159134165897</v>
       </c>
     </row>
     <row r="918">
@@ -11093,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.25229799526824</v>
+        <v>-0.260356643952949</v>
       </c>
     </row>
     <row r="919">
@@ -11104,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.20189034664387</v>
+        <v>-1.18507709741097</v>
       </c>
     </row>
     <row r="920">
@@ -11115,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.379788260314455</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="921">
@@ -11137,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.166391516932209</v>
+        <v>-0.314817397069392</v>
       </c>
     </row>
     <row r="923">
@@ -11159,7 +11162,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.19152669263732</v>
       </c>
     </row>
     <row r="925">
@@ -11170,7 +11173,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.364793200466733</v>
+        <v>-1.13641252769393</v>
       </c>
     </row>
     <row r="926">
@@ -11181,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.498626555732279</v>
+        <v>-0.19921312663373</v>
       </c>
     </row>
     <row r="927">
@@ -11192,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.16423261652364</v>
+        <v>-0.212070452869082</v>
       </c>
     </row>
     <row r="928">
@@ -11214,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.381864940224365</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="930">
@@ -11225,7 +11228,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-1.28370132773899</v>
+        <v>-0.707171842308016</v>
       </c>
     </row>
     <row r="931">
@@ -11236,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.174822319695234</v>
+        <v>-1.07070758696265</v>
       </c>
     </row>
     <row r="932">
@@ -11247,7 +11250,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-1.15629939035679</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="933">
@@ -11258,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.32739765333802</v>
+        <v>-1.23624873204974</v>
       </c>
     </row>
     <row r="934">
@@ -11269,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.214322265528933</v>
+        <v>-0.0826687984544161</v>
       </c>
     </row>
     <row r="935">
@@ -11280,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.23759394238609</v>
+        <v>-0.204243178757961</v>
       </c>
     </row>
     <row r="936">
@@ -11302,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.160488837005753</v>
+        <v>-0.345518755203432</v>
       </c>
     </row>
     <row r="938">
@@ -11313,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.226700008626055</v>
+        <v>-0.0932366471782153</v>
       </c>
     </row>
     <row r="939">
@@ -11324,7 +11327,7 @@
         <v>16</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.774189650924869</v>
       </c>
     </row>
     <row r="940">
@@ -11335,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.0488402612413981</v>
+        <v>-0.484380717620458</v>
       </c>
     </row>
     <row r="941">
@@ -11346,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.884202833661441</v>
+        <v>-0.206992810108446</v>
       </c>
     </row>
     <row r="942">
@@ -11357,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>0.226359615592149</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="943">
@@ -11368,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.730128545050339</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="944">
@@ -11379,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.59183596367844</v>
+        <v>-0.786250363384934</v>
       </c>
     </row>
     <row r="945">
@@ -11390,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.180537377563276</v>
+        <v>-0.176792731486686</v>
       </c>
     </row>
     <row r="946">
@@ -11412,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-1.32986767183092</v>
+        <v>-0.559213473821347</v>
       </c>
     </row>
     <row r="948">
@@ -11423,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.0296726864021262</v>
       </c>
     </row>
     <row r="949">
@@ -11434,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.608279451152805</v>
+        <v>-6.71560079965321</v>
       </c>
     </row>
     <row r="950">
@@ -11445,7 +11448,7 @@
         <v>16</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.437003803084295</v>
+        <v>-1.39931802800163</v>
       </c>
     </row>
     <row r="951">
@@ -11456,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.127367786150215</v>
+        <v>0.356137645820953</v>
       </c>
     </row>
     <row r="952">
@@ -11467,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>0.170904776299707</v>
+        <v>-0.0119071066285199</v>
       </c>
     </row>
     <row r="953">
@@ -11478,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.233432161991802</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="954">
@@ -11489,7 +11492,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.916858762279415</v>
+        <v>-0.45339106465068</v>
       </c>
     </row>
     <row r="955">
@@ -11522,7 +11525,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.181460343756909</v>
+        <v>-0.183549631213827</v>
       </c>
     </row>
     <row r="958">
@@ -11533,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>0.0683539832827373</v>
+        <v>-1.34995036240185</v>
       </c>
     </row>
     <row r="959">
@@ -11544,7 +11547,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.267250822717091</v>
+        <v>-0.177596542048633</v>
       </c>
     </row>
     <row r="960">
@@ -11555,7 +11558,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.601679683228687</v>
       </c>
     </row>
     <row r="961">
@@ -11588,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-2.84003615116994</v>
+        <v>-0.297638702544857</v>
       </c>
     </row>
     <row r="964">
@@ -11610,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>0.180632686389975</v>
+        <v>0.138403977552596</v>
       </c>
     </row>
     <row r="966">
@@ -11621,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.531238199376497</v>
+        <v>-0.351254831077822</v>
       </c>
     </row>
     <row r="967">
@@ -11632,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-3.25535708607792</v>
+        <v>-0.0470031154348987</v>
       </c>
     </row>
     <row r="968">
@@ -11654,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.15388577785535</v>
       </c>
     </row>
     <row r="970">
@@ -11665,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.240682244085332</v>
+        <v>-0.238869292254493</v>
       </c>
     </row>
     <row r="971">
@@ -11676,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.222092846110339</v>
+        <v>-0.267898077498019</v>
       </c>
     </row>
     <row r="972">
@@ -11687,7 +11690,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.188034219602934</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="973">
@@ -11709,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.330596016964914</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="975">
@@ -11731,7 +11734,7 @@
         <v>16</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.32384210191762</v>
       </c>
     </row>
     <row r="977">
@@ -11742,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.157190413014575</v>
+        <v>0.0707283884231213</v>
       </c>
     </row>
     <row r="978">
@@ -11753,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-1.25471374621105</v>
+        <v>0.00274945744063804</v>
       </c>
     </row>
     <row r="979">
@@ -11764,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.0749531537815977</v>
+        <v>-3.02955034543174</v>
       </c>
     </row>
     <row r="980">
@@ -11775,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.307474942345446</v>
+        <v>-0.220516063877513</v>
       </c>
     </row>
     <row r="981">
@@ -11786,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.190798286055408</v>
+        <v>-0.189395477651725</v>
       </c>
     </row>
     <row r="982">
@@ -11797,7 +11800,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.195365750200649</v>
+        <v>-0.164612593751642</v>
       </c>
     </row>
     <row r="983">
@@ -11808,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.175713341677646</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="984">
@@ -11819,7 +11822,7 @@
         <v>16</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.328724593107634</v>
+        <v>-0.75606554596607</v>
       </c>
     </row>
     <row r="985">
@@ -11830,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-1.29751613220937</v>
+        <v>-0.665614135865723</v>
       </c>
     </row>
     <row r="986">
@@ -11841,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-1.50685276397598</v>
+        <v>-0.971713242900703</v>
       </c>
     </row>
     <row r="987">
@@ -11852,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.5122465467272</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="988">
@@ -11863,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.2451207689384</v>
+        <v>-0.258326724401893</v>
       </c>
     </row>
     <row r="989">
@@ -11874,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.288094261581611</v>
+        <v>-3.98309056705742</v>
       </c>
     </row>
     <row r="990">
@@ -11885,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-1.14847113971683</v>
+        <v>-0.455505150316881</v>
       </c>
     </row>
     <row r="991">
@@ -11896,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.14795918367347</v>
+        <v>-3.05316482816362</v>
       </c>
     </row>
     <row r="992">
@@ -11907,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.163467403264592</v>
       </c>
     </row>
     <row r="993">
@@ -11918,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.723997208036324</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="994">
@@ -11929,7 +11932,7 @@
         <v>16</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.753427940081518</v>
       </c>
     </row>
     <row r="995">
@@ -11940,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.209647049949722</v>
+        <v>-1.87669983845775</v>
       </c>
     </row>
     <row r="996">
@@ -11951,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.840431356642376</v>
       </c>
     </row>
     <row r="997">
@@ -11962,7 +11965,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.499338407819085</v>
+        <v>-0.154813504610175</v>
       </c>
     </row>
     <row r="998">
@@ -11973,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.21271136076372</v>
+        <v>-0.203957021393482</v>
       </c>
     </row>
     <row r="999">
@@ -12006,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-1.05637105175253</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="1002">
@@ -12017,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.53178045998215</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1003">
@@ -12050,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.408269874126473</v>
+        <v>-0.23123667852623</v>
       </c>
     </row>
     <row r="1006">
@@ -12061,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.500615259474915</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1007">
@@ -12072,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.210281291083292</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1008">
@@ -12083,7 +12086,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.325561591217345</v>
       </c>
     </row>
     <row r="1009">
@@ -12094,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.162910542174967</v>
+        <v>-0.81336481539627</v>
       </c>
     </row>
     <row r="1010">
@@ -12105,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.343103931388989</v>
+        <v>-0.62848217431235</v>
       </c>
     </row>
     <row r="1011">
@@ -12116,7 +12119,7 @@
         <v>16</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.26462029402051</v>
       </c>
     </row>
     <row r="1012">
@@ -12138,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.499909127291774</v>
+        <v>-0.503183780621952</v>
       </c>
     </row>
     <row r="1014">
@@ -12149,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.219381763196838</v>
+        <v>-0.18910427693901</v>
       </c>
     </row>
     <row r="1015">
@@ -12160,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.191166342294853</v>
+        <v>-0.414534570617766</v>
       </c>
     </row>
     <row r="1016">
@@ -12171,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.242726721185007</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1017">
@@ -12204,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.287390729218271</v>
+        <v>-0.111425976208271</v>
       </c>
     </row>
     <row r="1020">
@@ -12215,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.240710346332306</v>
+        <v>-0.221735566821784</v>
       </c>
     </row>
     <row r="1021">
@@ -12226,7 +12229,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.466590151817654</v>
+        <v>-0.616193240403568</v>
       </c>
     </row>
     <row r="1022">
@@ -12237,7 +12240,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.387762957417478</v>
+        <v>-0.155537467381122</v>
       </c>
     </row>
     <row r="1023">
@@ -12248,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.556681010642181</v>
+        <v>-1.10321159619626</v>
       </c>
     </row>
     <row r="1024">
@@ -12259,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.135666429622992</v>
+        <v>-0.159255098292125</v>
       </c>
     </row>
     <row r="1025">
@@ -12270,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.618915082582414</v>
+        <v>-0.674125499131005</v>
       </c>
     </row>
     <row r="1026">
@@ -12281,7 +12284,7 @@
         <v>16</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.210704657882988</v>
+        <v>-0.357637045482062</v>
       </c>
     </row>
     <row r="1027">
@@ -12292,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.518659364470334</v>
+        <v>0.0694944734915972</v>
       </c>
     </row>
     <row r="1028">
@@ -12303,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.175277498934804</v>
+        <v>-0.199103364574142</v>
       </c>
     </row>
     <row r="1029">
@@ -12325,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.115823266521396</v>
+        <v>-0.682995599232251</v>
       </c>
     </row>
     <row r="1031">
@@ -12336,7 +12339,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.979574419906358</v>
       </c>
     </row>
     <row r="1032">
@@ -12380,7 +12383,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.42575435183826</v>
       </c>
     </row>
     <row r="1036">
@@ -12391,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.282676750486891</v>
+        <v>-0.3530032159649</v>
       </c>
     </row>
     <row r="1037">
@@ -12424,7 +12427,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.708778993283639</v>
+        <v>-0.80934038370836</v>
       </c>
     </row>
     <row r="1040">
@@ -12435,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.346387375911613</v>
+        <v>-0.335662088698249</v>
       </c>
     </row>
     <row r="1041">
@@ -12446,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.204222326893457</v>
       </c>
     </row>
     <row r="1042">
@@ -12457,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.242445109775214</v>
+        <v>-0.331755772610772</v>
       </c>
     </row>
     <row r="1043">
@@ -12468,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.992176998838308</v>
+        <v>-0.565758744241883</v>
       </c>
     </row>
     <row r="1044">
@@ -12479,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.424094604439423</v>
+        <v>-0.323042777251929</v>
       </c>
     </row>
     <row r="1045">
@@ -12490,7 +12493,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.159763313609467</v>
+        <v>-20.032737080451</v>
       </c>
     </row>
     <row r="1046">
@@ -12501,7 +12504,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.297935422537851</v>
+        <v>-0.169481325556602</v>
       </c>
     </row>
     <row r="1047">
@@ -12512,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.286743703554009</v>
+        <v>-0.140143374107508</v>
       </c>
     </row>
     <row r="1048">
@@ -12523,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.26336108637524</v>
       </c>
     </row>
     <row r="1049">
@@ -12534,7 +12537,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.352573832508186</v>
+        <v>-0.513034363267844</v>
       </c>
     </row>
     <row r="1050">
@@ -12545,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.449148999958174</v>
+        <v>-0.401070348632089</v>
       </c>
     </row>
     <row r="1051">
@@ -12556,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.901450083059051</v>
+        <v>-0.876518943298273</v>
       </c>
     </row>
     <row r="1052">
@@ -12567,7 +12570,7 @@
         <v>16</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.73262376365698</v>
       </c>
     </row>
     <row r="1053">
@@ -12578,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.306119608656041</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1054">
@@ -12589,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.875901104471152</v>
+        <v>-0.703523766326817</v>
       </c>
     </row>
     <row r="1055">
@@ -12622,7 +12625,7 @@
         <v>16</v>
       </c>
       <c r="C1057" t="n">
-        <v>-1.57798675517649</v>
+        <v>-1.06986819194304</v>
       </c>
     </row>
     <row r="1058">
@@ -12633,7 +12636,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.322930731677981</v>
+        <v>-0.322618524168312</v>
       </c>
     </row>
     <row r="1059">
@@ -12644,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.00931321881317526</v>
+        <v>-0.305277671927784</v>
       </c>
     </row>
     <row r="1060">
@@ -12655,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.853538509589358</v>
+        <v>-0.791280059389956</v>
       </c>
     </row>
     <row r="1061">
@@ -12666,7 +12669,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.627075160857757</v>
+        <v>-0.913405479913718</v>
       </c>
     </row>
     <row r="1062">
@@ -12677,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.397171511222865</v>
+        <v>-1.0311341054055</v>
       </c>
     </row>
     <row r="1063">
@@ -12688,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.263301098315107</v>
+        <v>-0.23604152957615</v>
       </c>
     </row>
     <row r="1064">
@@ -12699,7 +12702,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.609000510825842</v>
+        <v>-0.763946700423552</v>
       </c>
     </row>
     <row r="1065">
@@ -12710,7 +12713,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.174395822595115</v>
       </c>
     </row>
     <row r="1066">
@@ -12721,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.255723659441737</v>
+        <v>-0.450474111288065</v>
       </c>
     </row>
     <row r="1067">
@@ -12732,7 +12735,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.213370531801302</v>
+        <v>-0.118493720389121</v>
       </c>
     </row>
     <row r="1068">
@@ -12743,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.158151991326378</v>
+        <v>-0.707351979511294</v>
       </c>
     </row>
     <row r="1069">
@@ -12754,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.34228675413443</v>
+        <v>-0.279771280738503</v>
       </c>
     </row>
     <row r="1070">
@@ -12776,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-1.22272457643948</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1072">
@@ -12787,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.474430264664128</v>
+        <v>-1.16228700351652</v>
       </c>
     </row>
     <row r="1073">
@@ -12820,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.902285088960323</v>
       </c>
     </row>
     <row r="1076">
@@ -12831,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.546929409698557</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1077">
@@ -12842,7 +12845,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.11651876653364</v>
       </c>
     </row>
     <row r="1078">
@@ -12853,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.203377651870903</v>
+        <v>-1.18888327924927</v>
       </c>
     </row>
     <row r="1079">
@@ -12864,7 +12867,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.68141145421676</v>
+        <v>-0.578195369124302</v>
       </c>
     </row>
     <row r="1080">
@@ -12875,7 +12878,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.546322994027627</v>
+        <v>-0.165742359211721</v>
       </c>
     </row>
     <row r="1081">
@@ -12886,7 +12889,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.78966614174439</v>
       </c>
     </row>
     <row r="1082">
@@ -12897,7 +12900,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.572689264257566</v>
       </c>
     </row>
     <row r="1083">
@@ -12919,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.787331334450421</v>
+        <v>-0.610170307156497</v>
       </c>
     </row>
     <row r="1085">
@@ -12930,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.00903727894328021</v>
+        <v>-0.222630210101211</v>
       </c>
     </row>
     <row r="1086">
@@ -12941,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.899207922383439</v>
       </c>
     </row>
     <row r="1087">
@@ -12974,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.132238909734345</v>
       </c>
     </row>
     <row r="1090">
@@ -12985,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.44246228119713</v>
+        <v>-1.05037384489691</v>
       </c>
     </row>
     <row r="1091">
@@ -13007,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.218568956193252</v>
+        <v>-0.0426842207611682</v>
       </c>
     </row>
     <row r="1093">
@@ -13018,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.920080827235885</v>
+        <v>-0.210365172150799</v>
       </c>
     </row>
     <row r="1094">
@@ -13029,7 +13032,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.946501809573828</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1095">
@@ -13040,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.688998338849047</v>
+        <v>-0.236202619157091</v>
       </c>
     </row>
     <row r="1096">
@@ -13084,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.265111623632835</v>
+        <v>-0.564477909823065</v>
       </c>
     </row>
     <row r="1100">
@@ -13095,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.376618999712877</v>
+        <v>-0.237019040888766</v>
       </c>
     </row>
     <row r="1101">
@@ -13106,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.303972393411388</v>
+        <v>-0.41282099715925</v>
       </c>
     </row>
     <row r="1102">
@@ -13117,7 +13120,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.1664708853485</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1103">
@@ -13128,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.244136300139642</v>
+        <v>-0.293019142240576</v>
       </c>
     </row>
     <row r="1104">
@@ -13139,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.617055072823612</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1105">
@@ -13150,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.164858733635514</v>
+        <v>-0.161065814314391</v>
       </c>
     </row>
     <row r="1106">
@@ -13161,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.76270253908311</v>
       </c>
     </row>
     <row r="1107">
@@ -13172,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.543250119263394</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1108">
@@ -13183,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.170704301815231</v>
       </c>
     </row>
     <row r="1109">
@@ -13194,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.219405488211326</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1110">
@@ -13205,7 +13208,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.178671604839104</v>
+        <v>-0.44837686172205</v>
       </c>
     </row>
     <row r="1111">
@@ -13227,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.636762680435696</v>
+        <v>-0.397925234546326</v>
       </c>
     </row>
     <row r="1113">
@@ -13238,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.660000733409454</v>
+        <v>-0.355830886779324</v>
       </c>
     </row>
     <row r="1114">
@@ -13249,7 +13252,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.494691615643384</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1115">
@@ -13260,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.187569512189906</v>
+        <v>-0.23630639346454</v>
       </c>
     </row>
     <row r="1116">
@@ -13271,7 +13274,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.29541623906512</v>
       </c>
     </row>
     <row r="1117">
@@ -13282,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.357524479810494</v>
+        <v>-2.78651165864739</v>
       </c>
     </row>
     <row r="1118">
@@ -13293,7 +13296,7 @@
         <v>16</v>
       </c>
       <c r="C1118" t="n">
-        <v>-0.430738950429609</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1119">
@@ -13304,7 +13307,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.30213806432003</v>
+        <v>-0.795229062137725</v>
       </c>
     </row>
     <row r="1120">
@@ -13326,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.46132435824858</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1122">
@@ -13337,7 +13340,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.278584008473584</v>
+        <v>-0.592586663824925</v>
       </c>
     </row>
     <row r="1123">
@@ -13348,7 +13351,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.339755552550621</v>
       </c>
     </row>
     <row r="1124">
@@ -13381,7 +13384,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.317182614910826</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1127">
@@ -13392,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.174983831369617</v>
+        <v>-9.43405549447826</v>
       </c>
     </row>
     <row r="1128">
@@ -13403,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.694091345907913</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1129">
@@ -13414,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.21028537711828</v>
+        <v>-0.00771942745560117</v>
       </c>
     </row>
     <row r="1130">
@@ -13425,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.305681102875461</v>
+        <v>-0.175723055213444</v>
       </c>
     </row>
     <row r="1131">
@@ -13436,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.524355011992752</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1132">
@@ -13491,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.22349605944836</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1137">
@@ -13502,7 +13505,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-1.23113289954052</v>
+        <v>-0.895398128091356</v>
       </c>
     </row>
     <row r="1138">
@@ -13524,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.301357735004872</v>
       </c>
     </row>
     <row r="1140">
@@ -13546,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.292660433093216</v>
+        <v>-0.899220552206054</v>
       </c>
     </row>
     <row r="1142">
@@ -13557,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.242623127081883</v>
+        <v>-0.192840824939718</v>
       </c>
     </row>
     <row r="1143">
@@ -13568,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.102665421284044</v>
       </c>
     </row>
     <row r="1144">
@@ -13579,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.17563082682987</v>
+        <v>-0.357749860736202</v>
       </c>
     </row>
     <row r="1145">
@@ -13590,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.62911189228133</v>
+        <v>-0.202005921608181</v>
       </c>
     </row>
     <row r="1146">
@@ -13601,7 +13604,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.218157063412579</v>
+        <v>-0.339523416436147</v>
       </c>
     </row>
     <row r="1147">
@@ -13612,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.774854973284591</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1148">
@@ -13623,7 +13626,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.159763313609467</v>
+        <v>-5.5748910387558</v>
       </c>
     </row>
     <row r="1149">
@@ -13634,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.213722988025832</v>
       </c>
     </row>
     <row r="1150">
@@ -13645,7 +13648,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.197441194552297</v>
+        <v>-0.227055825867858</v>
       </c>
     </row>
     <row r="1151">
@@ -13656,7 +13659,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.242600812288185</v>
+        <v>-0.141188780963907</v>
       </c>
     </row>
     <row r="1152">
@@ -13689,7 +13692,7 @@
         <v>16</v>
       </c>
       <c r="C1154" t="n">
-        <v>-4.47755194990682</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1155">
@@ -13711,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.769663288640521</v>
       </c>
     </row>
     <row r="1157">
@@ -13733,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.18125265959913</v>
+        <v>-0.140655036848331</v>
       </c>
     </row>
     <row r="1159">
@@ -13744,7 +13747,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.885334839404559</v>
+        <v>-0.469998250576173</v>
       </c>
     </row>
     <row r="1160">
@@ -13755,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.459383356580924</v>
+        <v>-0.649523930289105</v>
       </c>
     </row>
     <row r="1161">
@@ -13766,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.0888429847698653</v>
+        <v>0.344091554354282</v>
       </c>
     </row>
     <row r="1162">
@@ -13777,7 +13780,7 @@
         <v>16</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.520769906744023</v>
+        <v>-1.23158566209681</v>
       </c>
     </row>
     <row r="1163">
@@ -13799,7 +13802,7 @@
         <v>16</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.188480383188122</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1165">
@@ -13810,7 +13813,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-2.42270772756706</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1166">
@@ -13821,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.435286768254453</v>
+        <v>-0.329117559688924</v>
       </c>
     </row>
     <row r="1167">
@@ -13832,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.55135587944836</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1168">
@@ -13854,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.550681827252397</v>
+        <v>-0.245108242784256</v>
       </c>
     </row>
     <row r="1170">
@@ -13865,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.183446035455859</v>
+        <v>-0.0331887332229144</v>
       </c>
     </row>
     <row r="1171">
@@ -13876,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.19976457372997</v>
+        <v>-0.33841245588986</v>
       </c>
     </row>
     <row r="1172">
@@ -13887,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.469482657921294</v>
+        <v>-0.188974342842696</v>
       </c>
     </row>
     <row r="1173">
@@ -13920,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.382783876351724</v>
+        <v>-0.308582811442966</v>
       </c>
     </row>
     <row r="1176">
@@ -13931,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.611270143526528</v>
+        <v>-0.425806890071823</v>
       </c>
     </row>
     <row r="1177">
@@ -13953,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.549607084402856</v>
+        <v>-0.171589146035258</v>
       </c>
     </row>
     <row r="1179">
@@ -13975,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.174785053047277</v>
       </c>
     </row>
     <row r="1181">
@@ -13986,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.227430488825902</v>
+        <v>-0.144906170138402</v>
       </c>
     </row>
     <row r="1182">
@@ -13997,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.283767147883124</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1183">
@@ -14008,7 +14011,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.375479130364212</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1184">
@@ -14019,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.143641779225259</v>
+        <v>-0.180207899455411</v>
       </c>
     </row>
     <row r="1185">
@@ -14030,7 +14033,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.388986602508126</v>
+        <v>-0.640131701508792</v>
       </c>
     </row>
     <row r="1186">
@@ -14041,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.207489084198006</v>
+        <v>-0.305073119564113</v>
       </c>
     </row>
     <row r="1187">
@@ -14063,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.249796162246905</v>
+        <v>-0.698080754524302</v>
       </c>
     </row>
     <row r="1189">
@@ -14074,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.165305995557545</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1190">
@@ -14085,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.786313655909316</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1191">
@@ -14107,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.33342627674964</v>
       </c>
     </row>
     <row r="1193">
@@ -14118,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.330434984535932</v>
+        <v>-1.00342946114495</v>
       </c>
     </row>
     <row r="1194">
@@ -14129,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.882246979124412</v>
+        <v>-0.0886819767819402</v>
       </c>
     </row>
     <row r="1195">
@@ -14140,7 +14143,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.337104379192144</v>
+        <v>-0.475927511732377</v>
       </c>
     </row>
     <row r="1196">
@@ -14162,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.385675351389416</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1198">
@@ -14184,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.951860968669857</v>
       </c>
     </row>
     <row r="1200">
@@ -14195,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-1.57791279595337</v>
+        <v>-0.216313971747689</v>
       </c>
     </row>
     <row r="1201">
@@ -14206,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.57528267078783</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
   </sheetData>
@@ -14268,7 +14271,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>4.135</v>
+        <v>3.32626319043006</v>
       </c>
     </row>
     <row r="4">
@@ -14761,7 +14764,7 @@
         <v>517.34</v>
       </c>
       <c r="E32" t="n">
-        <v>58.8892857142856</v>
+        <v>11821.1925467796</v>
       </c>
     </row>
     <row r="33">
@@ -14863,7 +14866,7 @@
         <v>882.37</v>
       </c>
       <c r="E38" t="n">
-        <v>32.8157142857142</v>
+        <v>4850.33271391602</v>
       </c>
     </row>
     <row r="39">
@@ -14982,7 +14985,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E45" t="n">
-        <v>202.409285714286</v>
+        <v>2981.67137243695</v>
       </c>
     </row>
     <row r="46">
@@ -15373,7 +15376,7 @@
         <v>65</v>
       </c>
       <c r="E68" t="n">
-        <v>42.5</v>
+        <v>125.63163864022</v>
       </c>
     </row>
     <row r="69">
@@ -15611,7 +15614,7 @@
         <v>8</v>
       </c>
       <c r="E82" t="n">
-        <v>9.69459090367471</v>
+        <v>10.7437814361532</v>
       </c>
     </row>
     <row r="83">
@@ -15679,7 +15682,7 @@
         <v>6</v>
       </c>
       <c r="E86" t="n">
-        <v>17.2772469736179</v>
+        <v>9.07692307692308</v>
       </c>
     </row>
     <row r="87">
@@ -15696,7 +15699,7 @@
         <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>8.30769230769231</v>
+        <v>63.6655775118336</v>
       </c>
     </row>
     <row r="88">
@@ -15730,7 +15733,7 @@
         <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>6.13446094897956</v>
+        <v>8.38461538461539</v>
       </c>
     </row>
     <row r="90">
@@ -15763,189 +15766,750 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>42</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" t="n">
-        <v>0.214285714285714</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>47</v>
       </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
       <c r="D6" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>48</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
+      <c r="E7" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
+      <c r="E8" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+      <c r="E9" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
+      <c r="E10" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.133333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.133333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.133333333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.0714285714285714</v>
       </c>
-      <c r="E11" t="s">
-        <v>21</v>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0714285714285714</v>
       </c>
     </row>
   </sheetData>
